--- a/data/NREL-118/Power_ThermalGen.xlsx
+++ b/data/NREL-118/Power_ThermalGen.xlsx
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>3</v>
@@ -1493,10 +1493,10 @@
         <v/>
       </c>
       <c r="V8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X8" s="16" t="n">
         <v/>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>3</v>
@@ -1596,10 +1596,10 @@
         <v/>
       </c>
       <c r="V9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X9" s="16" t="n">
         <v/>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>1.2</v>
@@ -1699,10 +1699,10 @@
         <v/>
       </c>
       <c r="V10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X10" s="16" t="n">
         <v/>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>1.2</v>
@@ -1802,10 +1802,10 @@
         <v/>
       </c>
       <c r="V11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X11" s="16" t="n">
         <v/>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>1.3</v>
@@ -1905,10 +1905,10 @@
         <v/>
       </c>
       <c r="V12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X12" s="16" t="n">
         <v/>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>1.3</v>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="V13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X13" s="16" t="n">
         <v/>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>3</v>
@@ -2111,10 +2111,10 @@
         <v/>
       </c>
       <c r="V14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X14" s="16" t="n">
         <v/>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>1.35</v>
@@ -2214,10 +2214,10 @@
         <v/>
       </c>
       <c r="V15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X15" s="16" t="n">
         <v/>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>1.35</v>
@@ -2317,10 +2317,10 @@
         <v/>
       </c>
       <c r="V16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X16" s="16" t="n">
         <v/>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>1.35</v>
@@ -2420,10 +2420,10 @@
         <v/>
       </c>
       <c r="V17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X17" s="16" t="n">
         <v/>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>0.71</v>
@@ -2523,10 +2523,10 @@
         <v/>
       </c>
       <c r="V18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X18" s="16" t="n">
         <v/>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>0.71</v>
@@ -2626,10 +2626,10 @@
         <v/>
       </c>
       <c r="V19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X19" s="16" t="n">
         <v/>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>0.71</v>
@@ -2729,10 +2729,10 @@
         <v/>
       </c>
       <c r="V20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X20" s="16" t="n">
         <v/>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>1.57</v>
@@ -2832,10 +2832,10 @@
         <v/>
       </c>
       <c r="V21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X21" s="16" t="n">
         <v/>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>0.65</v>
@@ -2935,10 +2935,10 @@
         <v/>
       </c>
       <c r="V22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X22" s="16" t="n">
         <v/>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>0.65</v>
@@ -3038,10 +3038,10 @@
         <v/>
       </c>
       <c r="V23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X23" s="16" t="n">
         <v/>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>0.65</v>
@@ -3141,10 +3141,10 @@
         <v/>
       </c>
       <c r="V24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X24" s="16" t="n">
         <v/>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>0.65</v>
@@ -3244,10 +3244,10 @@
         <v/>
       </c>
       <c r="V25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X25" s="16" t="n">
         <v/>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>0.45</v>
@@ -3347,10 +3347,10 @@
         <v/>
       </c>
       <c r="V26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X26" s="16" t="n">
         <v/>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>0.45</v>
@@ -3450,10 +3450,10 @@
         <v/>
       </c>
       <c r="V27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X27" s="16" t="n">
         <v/>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>0.45</v>
@@ -3553,10 +3553,10 @@
         <v/>
       </c>
       <c r="V28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X28" s="16" t="n">
         <v/>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>0.45</v>
@@ -3656,10 +3656,10 @@
         <v/>
       </c>
       <c r="V29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X29" s="16" t="n">
         <v/>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>1</v>
@@ -3759,10 +3759,10 @@
         <v/>
       </c>
       <c r="V30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X30" s="16" t="n">
         <v/>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>1</v>
@@ -3862,10 +3862,10 @@
         <v/>
       </c>
       <c r="V31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X31" s="16" t="n">
         <v/>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>1</v>
@@ -3965,10 +3965,10 @@
         <v/>
       </c>
       <c r="V32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X32" s="16" t="n">
         <v/>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>1.9</v>
@@ -4068,10 +4068,10 @@
         <v/>
       </c>
       <c r="V33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X33" s="16" t="n">
         <v/>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>1.9</v>
@@ -4171,10 +4171,10 @@
         <v/>
       </c>
       <c r="V34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X34" s="16" t="n">
         <v/>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>1.9</v>
@@ -4274,10 +4274,10 @@
         <v/>
       </c>
       <c r="V35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X35" s="16" t="n">
         <v/>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>1.9</v>
@@ -4377,10 +4377,10 @@
         <v/>
       </c>
       <c r="V36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X36" s="16" t="n">
         <v/>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>1.9</v>
@@ -4480,10 +4480,10 @@
         <v/>
       </c>
       <c r="V37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X37" s="16" t="n">
         <v/>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>1.9</v>
@@ -4583,10 +4583,10 @@
         <v/>
       </c>
       <c r="V38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X38" s="16" t="n">
         <v/>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1.9</v>
@@ -4686,10 +4686,10 @@
         <v/>
       </c>
       <c r="V39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X39" s="16" t="n">
         <v/>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>1.6</v>
@@ -4789,10 +4789,10 @@
         <v/>
       </c>
       <c r="V40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X40" s="16" t="n">
         <v/>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1.6</v>
@@ -4892,10 +4892,10 @@
         <v/>
       </c>
       <c r="V41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X41" s="16" t="n">
         <v/>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>1.6</v>
@@ -4995,10 +4995,10 @@
         <v/>
       </c>
       <c r="V42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X42" s="16" t="n">
         <v/>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>1.6</v>
@@ -5098,10 +5098,10 @@
         <v/>
       </c>
       <c r="V43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X43" s="16" t="n">
         <v/>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>0.95</v>
@@ -5201,10 +5201,10 @@
         <v/>
       </c>
       <c r="V44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X44" s="16" t="n">
         <v/>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>0.95</v>
@@ -5304,10 +5304,10 @@
         <v/>
       </c>
       <c r="V45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X45" s="16" t="n">
         <v/>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>0.95</v>
@@ -5407,10 +5407,10 @@
         <v/>
       </c>
       <c r="V46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X46" s="16" t="n">
         <v/>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>0.95</v>
@@ -5510,10 +5510,10 @@
         <v/>
       </c>
       <c r="V47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X47" s="16" t="n">
         <v/>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>1.88</v>
@@ -5613,10 +5613,10 @@
         <v/>
       </c>
       <c r="V48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X48" s="16" t="n">
         <v/>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1.88</v>
@@ -5716,10 +5716,10 @@
         <v/>
       </c>
       <c r="V49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X49" s="16" t="n">
         <v/>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>3.75</v>
@@ -5819,10 +5819,10 @@
         <v/>
       </c>
       <c r="V50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X50" s="16" t="n">
         <v/>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>2.29</v>
@@ -5922,10 +5922,10 @@
         <v/>
       </c>
       <c r="V51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X51" s="16" t="n">
         <v/>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>2.29</v>
@@ -6025,10 +6025,10 @@
         <v/>
       </c>
       <c r="V52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X52" s="16" t="n">
         <v/>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>1.2</v>
@@ -6128,10 +6128,10 @@
         <v/>
       </c>
       <c r="V53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X53" s="16" t="n">
         <v/>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>3</v>
@@ -6231,10 +6231,10 @@
         <v/>
       </c>
       <c r="V54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X54" s="16" t="n">
         <v/>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>3</v>
@@ -6334,10 +6334,10 @@
         <v/>
       </c>
       <c r="V55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X55" s="16" t="n">
         <v/>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>1.6</v>
@@ -6437,10 +6437,10 @@
         <v/>
       </c>
       <c r="V56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X56" s="16" t="n">
         <v/>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>0.9</v>
@@ -6540,10 +6540,10 @@
         <v/>
       </c>
       <c r="V57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X57" s="16" t="n">
         <v/>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>0.9</v>
@@ -6643,10 +6643,10 @@
         <v/>
       </c>
       <c r="V58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X58" s="16" t="n">
         <v/>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>3</v>
@@ -6746,10 +6746,10 @@
         <v/>
       </c>
       <c r="V59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X59" s="16" t="n">
         <v/>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>3</v>
@@ -6849,10 +6849,10 @@
         <v/>
       </c>
       <c r="V60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X60" s="16" t="n">
         <v/>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>3</v>
@@ -6952,10 +6952,10 @@
         <v/>
       </c>
       <c r="V61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X61" s="16" t="n">
         <v/>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>3</v>
@@ -7055,10 +7055,10 @@
         <v/>
       </c>
       <c r="V62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X62" s="16" t="n">
         <v/>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>4.6</v>
@@ -7158,10 +7158,10 @@
         <v/>
       </c>
       <c r="V63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X63" s="16" t="n">
         <v/>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>3</v>
@@ -7261,10 +7261,10 @@
         <v/>
       </c>
       <c r="V64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X64" s="16" t="n">
         <v/>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>3</v>
@@ -7364,10 +7364,10 @@
         <v/>
       </c>
       <c r="V65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X65" s="16" t="n">
         <v/>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>4.6</v>
@@ -7467,10 +7467,10 @@
         <v/>
       </c>
       <c r="V66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X66" s="16" t="n">
         <v/>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>3</v>
@@ -7570,10 +7570,10 @@
         <v/>
       </c>
       <c r="V67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X67" s="16" t="n">
         <v/>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>1.88</v>
@@ -7673,10 +7673,10 @@
         <v/>
       </c>
       <c r="V68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X68" s="16" t="n">
         <v/>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>7.5</v>
@@ -7776,10 +7776,10 @@
         <v/>
       </c>
       <c r="V69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="15" t="n">
-        <v>0</v>
+        <v>294201.0511702557</v>
       </c>
       <c r="X69" s="16" t="n">
         <v/>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>41.5</v>
@@ -7879,10 +7879,10 @@
         <v/>
       </c>
       <c r="V70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X70" s="16" t="n">
         <v/>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>126.98</v>
@@ -7982,10 +7982,10 @@
         <v/>
       </c>
       <c r="V71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X71" s="16" t="n">
         <v/>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>320</v>
@@ -8085,10 +8085,10 @@
         <v/>
       </c>
       <c r="V72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X72" s="16" t="n">
         <v/>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>100</v>
@@ -8188,10 +8188,10 @@
         <v/>
       </c>
       <c r="V73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X73" s="16" t="n">
         <v/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>13.5</v>
@@ -8291,10 +8291,10 @@
         <v/>
       </c>
       <c r="V74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X74" s="16" t="n">
         <v/>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>55.1</v>
@@ -8394,10 +8394,10 @@
         <v/>
       </c>
       <c r="V75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X75" s="16" t="n">
         <v/>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>14.3</v>
@@ -8497,10 +8497,10 @@
         <v/>
       </c>
       <c r="V76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X76" s="16" t="n">
         <v/>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="14" t="n">
         <v>33</v>
@@ -8600,10 +8600,10 @@
         <v/>
       </c>
       <c r="V77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X77" s="16" t="n">
         <v/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="14" t="n">
         <v>71.51000000000001</v>
@@ -8703,10 +8703,10 @@
         <v/>
       </c>
       <c r="V78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X78" s="16" t="n">
         <v/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>596.4</v>
@@ -8806,10 +8806,10 @@
         <v/>
       </c>
       <c r="V79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X79" s="16" t="n">
         <v/>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="14" t="n">
         <v>150</v>
@@ -8909,10 +8909,10 @@
         <v/>
       </c>
       <c r="V80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X80" s="16" t="n">
         <v/>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>57.3</v>
@@ -9012,10 +9012,10 @@
         <v/>
       </c>
       <c r="V81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X81" s="16" t="n">
         <v/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>164.75</v>
@@ -9115,10 +9115,10 @@
         <v/>
       </c>
       <c r="V82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X82" s="16" t="n">
         <v/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>27</v>
@@ -9218,10 +9218,10 @@
         <v/>
       </c>
       <c r="V83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X83" s="16" t="n">
         <v/>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>943.5</v>
@@ -9321,10 +9321,10 @@
         <v/>
       </c>
       <c r="V84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X84" s="16" t="n">
         <v/>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="14" t="n">
         <v>154.4</v>
@@ -9424,10 +9424,10 @@
         <v/>
       </c>
       <c r="V85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X85" s="16" t="n">
         <v/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>619</v>
@@ -9527,10 +9527,10 @@
         <v/>
       </c>
       <c r="V86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X86" s="16" t="n">
         <v/>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>140</v>
@@ -9630,10 +9630,10 @@
         <v/>
       </c>
       <c r="V87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X87" s="16" t="n">
         <v/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>25.8</v>
@@ -9733,10 +9733,10 @@
         <v/>
       </c>
       <c r="V88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X88" s="16" t="n">
         <v/>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>315</v>
@@ -9836,10 +9836,10 @@
         <v/>
       </c>
       <c r="V89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X89" s="16" t="n">
         <v/>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>677.8</v>
@@ -9939,10 +9939,10 @@
         <v/>
       </c>
       <c r="V90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X90" s="16" t="n">
         <v/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>636</v>
@@ -10042,10 +10042,10 @@
         <v/>
       </c>
       <c r="V91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X91" s="16" t="n">
         <v/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>672.3</v>
@@ -10145,10 +10145,10 @@
         <v/>
       </c>
       <c r="V92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X92" s="16" t="n">
         <v/>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>32.49</v>
@@ -10248,10 +10248,10 @@
         <v/>
       </c>
       <c r="V93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X93" s="16" t="n">
         <v/>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>655</v>
@@ -10351,10 +10351,10 @@
         <v/>
       </c>
       <c r="V94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X94" s="16" t="n">
         <v/>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>34.5</v>
@@ -10454,10 +10454,10 @@
         <v/>
       </c>
       <c r="V95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X95" s="16" t="n">
         <v/>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>181.5</v>
@@ -10557,10 +10557,10 @@
         <v/>
       </c>
       <c r="V96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X96" s="16" t="n">
         <v/>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>49.9</v>
@@ -10660,10 +10660,10 @@
         <v/>
       </c>
       <c r="V97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X97" s="16" t="n">
         <v/>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>336.5</v>
@@ -10763,10 +10763,10 @@
         <v/>
       </c>
       <c r="V98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X98" s="16" t="n">
         <v/>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>38.55</v>
@@ -10866,10 +10866,10 @@
         <v/>
       </c>
       <c r="V99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X99" s="16" t="n">
         <v/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>24.88</v>
@@ -10969,10 +10969,10 @@
         <v/>
       </c>
       <c r="V100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X100" s="16" t="n">
         <v/>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="14" t="n">
         <v>688.3</v>
@@ -11072,10 +11072,10 @@
         <v/>
       </c>
       <c r="V101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X101" s="16" t="n">
         <v/>
@@ -11118,7 +11118,7 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>595</v>
@@ -11175,10 +11175,10 @@
         <v/>
       </c>
       <c r="V102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X102" s="16" t="n">
         <v/>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="14" t="n">
         <v>668</v>
@@ -11278,10 +11278,10 @@
         <v/>
       </c>
       <c r="V103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X103" s="16" t="n">
         <v/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="14" t="n">
         <v>636</v>
@@ -11381,10 +11381,10 @@
         <v/>
       </c>
       <c r="V104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X104" s="16" t="n">
         <v/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="14" t="n">
         <v>98.2</v>
@@ -11484,10 +11484,10 @@
         <v/>
       </c>
       <c r="V105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X105" s="16" t="n">
         <v/>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="14" t="n">
         <v>247</v>
@@ -11587,10 +11587,10 @@
         <v/>
       </c>
       <c r="V106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X106" s="16" t="n">
         <v/>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC Gas</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>751.1</v>
@@ -11690,10 +11690,10 @@
         <v/>
       </c>
       <c r="V107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="15" t="n">
-        <v>0</v>
+        <v>104788.0207833251</v>
       </c>
       <c r="X107" s="16" t="n">
         <v/>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>25.4</v>
@@ -11793,10 +11793,10 @@
         <v/>
       </c>
       <c r="V108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X108" s="16" t="n">
         <v/>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="14" t="n">
         <v>25.4</v>
@@ -11896,10 +11896,10 @@
         <v/>
       </c>
       <c r="V109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X109" s="16" t="n">
         <v/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="14" t="n">
         <v>24.75</v>
@@ -11999,10 +11999,10 @@
         <v/>
       </c>
       <c r="V110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X110" s="16" t="n">
         <v/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
@@ -12054,7 +12054,7 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="14" t="n">
         <v>24.75</v>
@@ -12102,10 +12102,10 @@
         <v/>
       </c>
       <c r="V111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X111" s="16" t="n">
         <v/>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="14" t="n">
         <v>49.9</v>
@@ -12205,10 +12205,10 @@
         <v/>
       </c>
       <c r="V112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W112" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X112" s="16" t="n">
         <v/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="14" t="n">
         <v>49.9</v>
@@ -12308,10 +12308,10 @@
         <v/>
       </c>
       <c r="V113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X113" s="16" t="n">
         <v/>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -12363,7 +12363,7 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="14" t="n">
         <v>49.9</v>
@@ -12411,10 +12411,10 @@
         <v/>
       </c>
       <c r="V114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X114" s="16" t="n">
         <v/>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" s="14" t="n">
         <v>50</v>
@@ -12514,10 +12514,10 @@
         <v/>
       </c>
       <c r="V115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X115" s="16" t="n">
         <v/>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="14" t="n">
         <v>50</v>
@@ -12617,10 +12617,10 @@
         <v/>
       </c>
       <c r="V116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W116" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X116" s="16" t="n">
         <v/>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>50</v>
@@ -12720,10 +12720,10 @@
         <v/>
       </c>
       <c r="V117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X117" s="16" t="n">
         <v/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>50</v>
@@ -12823,10 +12823,10 @@
         <v/>
       </c>
       <c r="V118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X118" s="16" t="n">
         <v/>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="14" t="n">
         <v>50</v>
@@ -12926,10 +12926,10 @@
         <v/>
       </c>
       <c r="V119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X119" s="16" t="n">
         <v/>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
@@ -12981,7 +12981,7 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="14" t="n">
         <v>21.6</v>
@@ -13029,10 +13029,10 @@
         <v/>
       </c>
       <c r="V120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X120" s="16" t="n">
         <v/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>21.6</v>
@@ -13132,10 +13132,10 @@
         <v/>
       </c>
       <c r="V121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X121" s="16" t="n">
         <v/>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>21.6</v>
@@ -13235,10 +13235,10 @@
         <v/>
       </c>
       <c r="V122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X122" s="16" t="n">
         <v/>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -13290,7 +13290,7 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="14" t="n">
         <v>49.9</v>
@@ -13338,10 +13338,10 @@
         <v/>
       </c>
       <c r="V123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X123" s="16" t="n">
         <v/>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="14" t="n">
         <v>6.9</v>
@@ -13441,10 +13441,10 @@
         <v/>
       </c>
       <c r="V124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X124" s="16" t="n">
         <v/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="14" t="n">
         <v>3.9</v>
@@ -13544,10 +13544,10 @@
         <v/>
       </c>
       <c r="V125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X125" s="16" t="n">
         <v/>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -13599,7 +13599,7 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="14" t="n">
         <v>3.9</v>
@@ -13647,10 +13647,10 @@
         <v/>
       </c>
       <c r="V126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X126" s="16" t="n">
         <v/>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -13702,7 +13702,7 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="14" t="n">
         <v>6.9</v>
@@ -13750,10 +13750,10 @@
         <v/>
       </c>
       <c r="V127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X127" s="16" t="n">
         <v/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="14" t="n">
         <v>100</v>
@@ -13853,10 +13853,10 @@
         <v/>
       </c>
       <c r="V128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X128" s="16" t="n">
         <v/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="14" t="n">
         <v>100</v>
@@ -13956,10 +13956,10 @@
         <v/>
       </c>
       <c r="V129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X129" s="16" t="n">
         <v/>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
@@ -14011,7 +14011,7 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="14" t="n">
         <v>100</v>
@@ -14059,10 +14059,10 @@
         <v/>
       </c>
       <c r="V130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X130" s="16" t="n">
         <v/>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="14" t="n">
         <v>100</v>
@@ -14162,10 +14162,10 @@
         <v/>
       </c>
       <c r="V131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X131" s="16" t="n">
         <v/>
@@ -14208,7 +14208,7 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="14" t="n">
         <v>100</v>
@@ -14265,10 +14265,10 @@
         <v/>
       </c>
       <c r="V132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X132" s="16" t="n">
         <v/>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="14" t="n">
         <v>100</v>
@@ -14368,10 +14368,10 @@
         <v/>
       </c>
       <c r="V133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X133" s="16" t="n">
         <v/>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="14" t="n">
         <v>1.05</v>
@@ -14471,10 +14471,10 @@
         <v/>
       </c>
       <c r="V134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X134" s="16" t="n">
         <v/>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" s="14" t="n">
         <v>44.02</v>
@@ -14574,10 +14574,10 @@
         <v/>
       </c>
       <c r="V135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X135" s="16" t="n">
         <v/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="14" t="n">
         <v>0.6</v>
@@ -14677,10 +14677,10 @@
         <v/>
       </c>
       <c r="V136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X136" s="16" t="n">
         <v/>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="14" t="n">
         <v>18</v>
@@ -14780,10 +14780,10 @@
         <v/>
       </c>
       <c r="V137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X137" s="16" t="n">
         <v/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
@@ -14835,7 +14835,7 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="14" t="n">
         <v>1.54</v>
@@ -14883,10 +14883,10 @@
         <v/>
       </c>
       <c r="V138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X138" s="16" t="n">
         <v/>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" s="14" t="n">
         <v>1.6</v>
@@ -14986,10 +14986,10 @@
         <v/>
       </c>
       <c r="V139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X139" s="16" t="n">
         <v/>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="14" t="n">
         <v>1.3</v>
@@ -15089,10 +15089,10 @@
         <v/>
       </c>
       <c r="V140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X140" s="16" t="n">
         <v/>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -15144,7 +15144,7 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" s="14" t="n">
         <v>100</v>
@@ -15192,10 +15192,10 @@
         <v/>
       </c>
       <c r="V141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X141" s="16" t="n">
         <v/>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="14" t="n">
         <v>100</v>
@@ -15295,10 +15295,10 @@
         <v/>
       </c>
       <c r="V142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X142" s="16" t="n">
         <v/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" s="14" t="n">
         <v>100</v>
@@ -15398,10 +15398,10 @@
         <v/>
       </c>
       <c r="V143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X143" s="16" t="n">
         <v/>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" s="14" t="n">
         <v>1.3</v>
@@ -15501,10 +15501,10 @@
         <v/>
       </c>
       <c r="V144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X144" s="16" t="n">
         <v/>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="14" t="n">
         <v>9.5</v>
@@ -15604,10 +15604,10 @@
         <v/>
       </c>
       <c r="V145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X145" s="16" t="n">
         <v/>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -15659,7 +15659,7 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" s="14" t="n">
         <v>1.3</v>
@@ -15707,10 +15707,10 @@
         <v/>
       </c>
       <c r="V146" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X146" s="16" t="n">
         <v/>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" s="14" t="n">
         <v>3.1</v>
@@ -15810,10 +15810,10 @@
         <v/>
       </c>
       <c r="V147" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X147" s="16" t="n">
         <v/>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -15865,7 +15865,7 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>54</v>
@@ -15913,10 +15913,10 @@
         <v/>
       </c>
       <c r="V148" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X148" s="16" t="n">
         <v/>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="F149" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" s="14" t="n">
         <v>82.40000000000001</v>
@@ -16016,10 +16016,10 @@
         <v/>
       </c>
       <c r="V149" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X149" s="16" t="n">
         <v/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="F150" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" s="14" t="n">
         <v>25</v>
@@ -16119,10 +16119,10 @@
         <v/>
       </c>
       <c r="V150" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X150" s="16" t="n">
         <v/>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
@@ -16174,7 +16174,7 @@
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" s="14" t="n">
         <v>60.35</v>
@@ -16222,10 +16222,10 @@
         <v/>
       </c>
       <c r="V151" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W151" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X151" s="16" t="n">
         <v/>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
@@ -16277,7 +16277,7 @@
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" s="14" t="n">
         <v>60.35</v>
@@ -16325,10 +16325,10 @@
         <v/>
       </c>
       <c r="V152" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W152" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X152" s="16" t="n">
         <v/>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="F153" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" s="14" t="n">
         <v>180</v>
@@ -16428,10 +16428,10 @@
         <v/>
       </c>
       <c r="V153" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X153" s="16" t="n">
         <v/>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -16483,7 +16483,7 @@
         </is>
       </c>
       <c r="F154" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="14" t="n">
         <v>180</v>
@@ -16531,10 +16531,10 @@
         <v/>
       </c>
       <c r="V154" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X154" s="16" t="n">
         <v/>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -16586,7 +16586,7 @@
         </is>
       </c>
       <c r="F155" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" s="14" t="n">
         <v>180</v>
@@ -16634,10 +16634,10 @@
         <v/>
       </c>
       <c r="V155" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X155" s="16" t="n">
         <v/>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -16689,7 +16689,7 @@
         </is>
       </c>
       <c r="F156" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" s="14" t="n">
         <v>180</v>
@@ -16737,10 +16737,10 @@
         <v/>
       </c>
       <c r="V156" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W156" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X156" s="16" t="n">
         <v/>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -16792,7 +16792,7 @@
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" s="14" t="n">
         <v>49.96</v>
@@ -16840,10 +16840,10 @@
         <v/>
       </c>
       <c r="V157" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X157" s="16" t="n">
         <v/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -16895,7 +16895,7 @@
         </is>
       </c>
       <c r="F158" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" s="14" t="n">
         <v>8.57</v>
@@ -16943,10 +16943,10 @@
         <v/>
       </c>
       <c r="V158" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X158" s="16" t="n">
         <v/>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="F159" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" s="14" t="n">
         <v>10.71</v>
@@ -17046,10 +17046,10 @@
         <v/>
       </c>
       <c r="V159" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W159" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X159" s="16" t="n">
         <v/>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -17101,7 +17101,7 @@
         </is>
       </c>
       <c r="F160" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" s="14" t="n">
         <v>10.71</v>
@@ -17149,10 +17149,10 @@
         <v/>
       </c>
       <c r="V160" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W160" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X160" s="16" t="n">
         <v/>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -17204,7 +17204,7 @@
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" s="14" t="n">
         <v>49.9</v>
@@ -17252,10 +17252,10 @@
         <v/>
       </c>
       <c r="V161" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X161" s="16" t="n">
         <v/>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" s="14" t="n">
         <v>15</v>
@@ -17355,10 +17355,10 @@
         <v/>
       </c>
       <c r="V162" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W162" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X162" s="16" t="n">
         <v/>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="F163" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" s="14" t="n">
         <v>46.9</v>
@@ -17458,10 +17458,10 @@
         <v/>
       </c>
       <c r="V163" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W163" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X163" s="16" t="n">
         <v/>
@@ -17504,7 +17504,7 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -17513,7 +17513,7 @@
         </is>
       </c>
       <c r="F164" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" s="14" t="n">
         <v>45</v>
@@ -17561,10 +17561,10 @@
         <v/>
       </c>
       <c r="V164" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W164" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X164" s="16" t="n">
         <v/>
@@ -17607,7 +17607,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="F165" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" s="14" t="n">
         <v>45</v>
@@ -17664,10 +17664,10 @@
         <v/>
       </c>
       <c r="V165" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W165" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X165" s="16" t="n">
         <v/>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" s="14" t="n">
         <v>46.7</v>
@@ -17767,10 +17767,10 @@
         <v/>
       </c>
       <c r="V166" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W166" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X166" s="16" t="n">
         <v/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" s="14" t="n">
         <v>49.5</v>
@@ -17870,10 +17870,10 @@
         <v/>
       </c>
       <c r="V167" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W167" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X167" s="16" t="n">
         <v/>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="F168" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" s="14" t="n">
         <v>44.02</v>
@@ -17973,10 +17973,10 @@
         <v/>
       </c>
       <c r="V168" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W168" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X168" s="16" t="n">
         <v/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G169" s="14" t="n">
         <v>44.02</v>
@@ -18076,10 +18076,10 @@
         <v/>
       </c>
       <c r="V169" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W169" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X169" s="16" t="n">
         <v/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -18131,7 +18131,7 @@
         </is>
       </c>
       <c r="F170" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" s="14" t="n">
         <v>50</v>
@@ -18179,10 +18179,10 @@
         <v/>
       </c>
       <c r="V170" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W170" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X170" s="16" t="n">
         <v/>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
@@ -18234,7 +18234,7 @@
         </is>
       </c>
       <c r="F171" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" s="14" t="n">
         <v>50</v>
@@ -18282,10 +18282,10 @@
         <v/>
       </c>
       <c r="V171" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W171" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X171" s="16" t="n">
         <v/>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="F172" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="14" t="n">
         <v>42</v>
@@ -18385,10 +18385,10 @@
         <v/>
       </c>
       <c r="V172" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W172" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X172" s="16" t="n">
         <v/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>OC Gas</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="F173" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="14" t="n">
         <v>50.4</v>
@@ -18488,10 +18488,10 @@
         <v/>
       </c>
       <c r="V173" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W173" s="15" t="n">
-        <v>0</v>
+        <v>47718.67056370105</v>
       </c>
       <c r="X173" s="16" t="n">
         <v/>
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="F174" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" s="14" t="n">
         <v>74.5</v>
@@ -18591,10 +18591,10 @@
         <v/>
       </c>
       <c r="V174" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W174" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X174" s="16" t="n">
         <v/>
@@ -18646,7 +18646,7 @@
         </is>
       </c>
       <c r="F175" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" s="14" t="n">
         <v>74.5</v>
@@ -18694,10 +18694,10 @@
         <v/>
       </c>
       <c r="V175" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W175" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X175" s="16" t="n">
         <v/>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="F176" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176" s="14" t="n">
         <v>74.5</v>
@@ -18797,10 +18797,10 @@
         <v/>
       </c>
       <c r="V176" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W176" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X176" s="16" t="n">
         <v/>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="F177" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177" s="14" t="n">
         <v>71.2</v>
@@ -18900,10 +18900,10 @@
         <v/>
       </c>
       <c r="V177" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W177" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X177" s="16" t="n">
         <v/>
@@ -18955,7 +18955,7 @@
         </is>
       </c>
       <c r="F178" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" s="14" t="n">
         <v>71.2</v>
@@ -19003,10 +19003,10 @@
         <v/>
       </c>
       <c r="V178" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W178" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X178" s="16" t="n">
         <v/>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr">
@@ -19161,7 +19161,7 @@
         </is>
       </c>
       <c r="F180" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" s="14" t="n">
         <v>3.25</v>
@@ -19209,10 +19209,10 @@
         <v/>
       </c>
       <c r="V180" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W180" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X180" s="16" t="n">
         <v/>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="F181" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="14" t="n">
         <v>8.4</v>
@@ -19312,10 +19312,10 @@
         <v/>
       </c>
       <c r="V181" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W181" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X181" s="16" t="n">
         <v/>
@@ -19358,7 +19358,7 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="F182" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="14" t="n">
         <v>8.4</v>
@@ -19415,10 +19415,10 @@
         <v/>
       </c>
       <c r="V182" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W182" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X182" s="16" t="n">
         <v/>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
@@ -19470,7 +19470,7 @@
         </is>
       </c>
       <c r="F183" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" s="14" t="n">
         <v>8.4</v>
@@ -19518,10 +19518,10 @@
         <v/>
       </c>
       <c r="V183" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W183" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X183" s="16" t="n">
         <v/>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -19573,7 +19573,7 @@
         </is>
       </c>
       <c r="F184" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" s="14" t="n">
         <v>8.4</v>
@@ -19621,10 +19621,10 @@
         <v/>
       </c>
       <c r="V184" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W184" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X184" s="16" t="n">
         <v/>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr">
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="F185" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" s="14" t="n">
         <v>8.4</v>
@@ -19724,10 +19724,10 @@
         <v/>
       </c>
       <c r="V185" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W185" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X185" s="16" t="n">
         <v/>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
@@ -19779,7 +19779,7 @@
         </is>
       </c>
       <c r="F186" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" s="14" t="n">
         <v>8.4</v>
@@ -19827,10 +19827,10 @@
         <v/>
       </c>
       <c r="V186" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W186" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X186" s="16" t="n">
         <v/>
@@ -19882,7 +19882,7 @@
         </is>
       </c>
       <c r="F187" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" s="14" t="n">
         <v>20</v>
@@ -19930,10 +19930,10 @@
         <v/>
       </c>
       <c r="V187" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W187" s="15" t="n">
-        <v>0</v>
+        <v>337208.0274480286</v>
       </c>
       <c r="X187" s="16" t="n">
         <v/>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
@@ -19985,7 +19985,7 @@
         </is>
       </c>
       <c r="F188" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" s="14" t="n">
         <v>320</v>
@@ -20033,10 +20033,10 @@
         <v/>
       </c>
       <c r="V188" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W188" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X188" s="16" t="n">
         <v/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr">
@@ -20088,7 +20088,7 @@
         </is>
       </c>
       <c r="F189" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" s="14" t="n">
         <v>325</v>
@@ -20136,10 +20136,10 @@
         <v/>
       </c>
       <c r="V189" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W189" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X189" s="16" t="n">
         <v/>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
@@ -20191,7 +20191,7 @@
         </is>
       </c>
       <c r="F190" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" s="14" t="n">
         <v>712</v>
@@ -20239,10 +20239,10 @@
         <v/>
       </c>
       <c r="V190" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W190" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X190" s="16" t="n">
         <v/>
@@ -20285,7 +20285,7 @@
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr">
@@ -20294,7 +20294,7 @@
         </is>
       </c>
       <c r="F191" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" s="14" t="n">
         <v>62.6</v>
@@ -20342,10 +20342,10 @@
         <v/>
       </c>
       <c r="V191" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X191" s="16" t="n">
         <v/>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="F192" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" s="14" t="n">
         <v>62.6</v>
@@ -20445,10 +20445,10 @@
         <v/>
       </c>
       <c r="V192" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W192" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X192" s="16" t="n">
         <v/>
@@ -20491,7 +20491,7 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
@@ -20500,7 +20500,7 @@
         </is>
       </c>
       <c r="F193" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" s="14" t="n">
         <v>110.25</v>
@@ -20548,10 +20548,10 @@
         <v/>
       </c>
       <c r="V193" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W193" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X193" s="16" t="n">
         <v/>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="F194" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" s="14" t="n">
         <v>110.25</v>
@@ -20651,10 +20651,10 @@
         <v/>
       </c>
       <c r="V194" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W194" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X194" s="16" t="n">
         <v/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="F195" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195" s="14" t="n">
         <v>306</v>
@@ -20754,10 +20754,10 @@
         <v/>
       </c>
       <c r="V195" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W195" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X195" s="16" t="n">
         <v/>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
@@ -20809,7 +20809,7 @@
         </is>
       </c>
       <c r="F196" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" s="14" t="n">
         <v>345.6</v>
@@ -20857,10 +20857,10 @@
         <v/>
       </c>
       <c r="V196" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W196" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X196" s="16" t="n">
         <v/>
@@ -20903,7 +20903,7 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
@@ -20912,7 +20912,7 @@
         </is>
       </c>
       <c r="F197" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197" s="14" t="n">
         <v>106.25</v>
@@ -20960,10 +20960,10 @@
         <v/>
       </c>
       <c r="V197" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W197" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X197" s="16" t="n">
         <v/>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="F198" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" s="14" t="n">
         <v>4.6</v>
@@ -21063,10 +21063,10 @@
         <v/>
       </c>
       <c r="V198" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W198" s="15" t="n">
-        <v>0</v>
+        <v>40086.59453558482</v>
       </c>
       <c r="X198" s="16" t="n">
         <v/>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CC/OC Gas</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr">
@@ -21118,7 +21118,7 @@
         </is>
       </c>
       <c r="F199" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" s="14" t="n">
         <v>30.4</v>
@@ -21166,10 +21166,10 @@
         <v/>
       </c>
       <c r="V199" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W199" s="15" t="n">
-        <v>0</v>
+        <v>76253.34567351307</v>
       </c>
       <c r="X199" s="16" t="n">
         <v/>

--- a/data/NREL-118/Power_ThermalGen.xlsx
+++ b/data/NREL-118/Power_ThermalGen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo\data\NREL-118\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75882C53-4F2B-4D00-AB0A-BE06A210BE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5FD69E-EC2B-4686-A02F-2D8F998F1DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -1161,26 +1161,31 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2170,8 +2175,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S8" s="15">
-        <f>0.004*1000</f>
-        <v>4</v>
+        <v>3.9824210027218383</v>
       </c>
       <c r="T8" s="15">
         <v>1.9411908214595739</v>
@@ -2181,8 +2185,7 @@
         <v>1</v>
       </c>
       <c r="W8" s="15">
-        <f>AVERAGE(3473,5788)*1000/25</f>
-        <v>185220</v>
+        <v>184666.74845471748</v>
       </c>
       <c r="X8" s="16"/>
       <c r="Y8" s="17"/>
@@ -2248,8 +2251,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S9" s="15">
-        <f t="shared" ref="S9:S69" si="1">0.004*1000</f>
-        <v>4</v>
+        <v>4.0039496520466225</v>
       </c>
       <c r="T9" s="15">
         <v>1.9411908214595739</v>
@@ -2259,8 +2261,7 @@
         <v>1</v>
       </c>
       <c r="W9" s="15">
-        <f t="shared" ref="W9:W69" si="2">AVERAGE(3473,5788)*1000/25</f>
-        <v>185220</v>
+        <v>184860.08757075731</v>
       </c>
       <c r="X9" s="16"/>
       <c r="Y9" s="17"/>
@@ -2326,8 +2327,7 @@
         <v>1.2775232512000001</v>
       </c>
       <c r="S10" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9829069815528921</v>
       </c>
       <c r="T10" s="15">
         <v>0.77647632858382953</v>
@@ -2337,8 +2337,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184423.92158394511</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="17"/>
@@ -2404,8 +2403,7 @@
         <v>1.2775232512000001</v>
       </c>
       <c r="S11" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0052200727620191</v>
       </c>
       <c r="T11" s="15">
         <v>0.77647632858382953</v>
@@ -2415,8 +2413,7 @@
         <v>1</v>
       </c>
       <c r="W11" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185440.48798366406</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="17"/>
@@ -2482,8 +2479,7 @@
         <v>1.3859369215999999</v>
       </c>
       <c r="S12" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0056040269827999</v>
       </c>
       <c r="T12" s="15">
         <v>0.84118268929914841</v>
@@ -2493,8 +2489,7 @@
         <v>1</v>
       </c>
       <c r="W12" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>186111.73087928019</v>
       </c>
       <c r="X12" s="16"/>
       <c r="Y12" s="17"/>
@@ -2560,8 +2555,7 @@
         <v>1.3859369215999999</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9824686359432255</v>
       </c>
       <c r="T13" s="15">
         <v>0.84118268929914841</v>
@@ -2571,8 +2565,7 @@
         <v>1</v>
       </c>
       <c r="W13" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184385.93239471485</v>
       </c>
       <c r="X13" s="16"/>
       <c r="Y13" s="17"/>
@@ -2638,8 +2631,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S14" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0045420558551923</v>
       </c>
       <c r="T14" s="15">
         <v>1.9411908214595739</v>
@@ -2649,8 +2641,7 @@
         <v>1</v>
       </c>
       <c r="W14" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185428.41300133633</v>
       </c>
       <c r="X14" s="16"/>
       <c r="Y14" s="17"/>
@@ -2716,8 +2707,7 @@
         <v>1.4386787072</v>
       </c>
       <c r="S15" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0055806646929266</v>
       </c>
       <c r="T15" s="15">
         <v>0.87414630702204699</v>
@@ -2727,8 +2717,7 @@
         <v>1</v>
       </c>
       <c r="W15" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185932.4922971307</v>
       </c>
       <c r="X15" s="16"/>
       <c r="Y15" s="17"/>
@@ -2794,8 +2783,7 @@
         <v>1.4386787072</v>
       </c>
       <c r="S16" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9839619911638229</v>
       </c>
       <c r="T16" s="15">
         <v>0.87414630702204699</v>
@@ -2805,8 +2793,7 @@
         <v>1</v>
       </c>
       <c r="W16" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185665.84996650089</v>
       </c>
       <c r="X16" s="16"/>
       <c r="Y16" s="17"/>
@@ -2872,8 +2859,7 @@
         <v>1.4386787072</v>
       </c>
       <c r="S17" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0151674547358471</v>
       </c>
       <c r="T17" s="15">
         <v>0.87414630702204699</v>
@@ -2883,8 +2869,7 @@
         <v>1</v>
       </c>
       <c r="W17" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185280.06418789006</v>
       </c>
       <c r="X17" s="16"/>
       <c r="Y17" s="17"/>
@@ -2950,8 +2935,7 @@
         <v>0.75596559360000004</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9963945962337881</v>
       </c>
       <c r="T18" s="15">
         <v>0.4590488986596224</v>
@@ -2961,8 +2945,7 @@
         <v>1</v>
       </c>
       <c r="W18" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184304.99147104379</v>
       </c>
       <c r="X18" s="16"/>
       <c r="Y18" s="17"/>
@@ -3028,8 +3011,7 @@
         <v>0.75596559360000004</v>
       </c>
       <c r="S19" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0113373747004966</v>
       </c>
       <c r="T19" s="15">
         <v>0.4590488986596224</v>
@@ -3039,8 +3021,7 @@
         <v>1</v>
       </c>
       <c r="W19" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185597.01936204784</v>
       </c>
       <c r="X19" s="16"/>
       <c r="Y19" s="17"/>
@@ -3106,8 +3087,7 @@
         <v>0.75596559360000004</v>
       </c>
       <c r="S20" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9981523889353205</v>
       </c>
       <c r="T20" s="15">
         <v>0.4590488986596224</v>
@@ -3117,8 +3097,7 @@
         <v>1</v>
       </c>
       <c r="W20" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185473.46578460344</v>
       </c>
       <c r="X20" s="16"/>
       <c r="Y20" s="17"/>
@@ -3184,8 +3163,7 @@
         <v>1.6730866432</v>
       </c>
       <c r="S21" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.998218018322079</v>
       </c>
       <c r="T21" s="15">
         <v>1.0157677757574619</v>
@@ -3195,8 +3173,7 @@
         <v>1</v>
       </c>
       <c r="W21" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185765.81836399017</v>
       </c>
       <c r="X21" s="16"/>
       <c r="Y21" s="17"/>
@@ -3262,8 +3239,7 @@
         <v>0.69150341119999992</v>
       </c>
       <c r="S22" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9832440709367489</v>
       </c>
       <c r="T22" s="15">
         <v>0.42120178201481312</v>
@@ -3273,8 +3249,7 @@
         <v>1</v>
       </c>
       <c r="W22" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185678.15336900807</v>
       </c>
       <c r="X22" s="16"/>
       <c r="Y22" s="17"/>
@@ -3340,8 +3315,7 @@
         <v>0.69150341119999992</v>
       </c>
       <c r="S23" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9814497963137945</v>
       </c>
       <c r="T23" s="15">
         <v>0.42120178201481312</v>
@@ -3351,8 +3325,7 @@
         <v>1</v>
       </c>
       <c r="W23" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185306.5407220909</v>
       </c>
       <c r="X23" s="16"/>
       <c r="Y23" s="17"/>
@@ -3418,8 +3391,7 @@
         <v>0.69150341119999992</v>
       </c>
       <c r="S24" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0168364421654346</v>
       </c>
       <c r="T24" s="15">
         <v>0.42120178201481312</v>
@@ -3429,8 +3401,7 @@
         <v>1</v>
       </c>
       <c r="W24" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184631.03104383819</v>
       </c>
       <c r="X24" s="16"/>
       <c r="Y24" s="17"/>
@@ -3496,8 +3467,7 @@
         <v>0.69150341119999992</v>
       </c>
       <c r="S25" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9957574467686103</v>
       </c>
       <c r="T25" s="15">
         <v>0.42120178201481312</v>
@@ -3507,8 +3477,7 @@
         <v>1</v>
       </c>
       <c r="W25" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185221.63609646552</v>
       </c>
       <c r="X25" s="16"/>
       <c r="Y25" s="17"/>
@@ -3574,8 +3543,7 @@
         <v>0.4805362688</v>
       </c>
       <c r="S26" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0073995890910741</v>
       </c>
       <c r="T26" s="15">
         <v>0.29178906058417492</v>
@@ -3585,8 +3553,7 @@
         <v>1</v>
       </c>
       <c r="W26" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185843.14775681982</v>
       </c>
       <c r="X26" s="16"/>
       <c r="Y26" s="17"/>
@@ -3652,8 +3619,7 @@
         <v>0.4805362688</v>
       </c>
       <c r="S27" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0016365745523554</v>
       </c>
       <c r="T27" s="15">
         <v>0.29178906058417492</v>
@@ -3663,8 +3629,7 @@
         <v>1</v>
       </c>
       <c r="W27" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185135.18010164241</v>
       </c>
       <c r="X27" s="16"/>
       <c r="Y27" s="17"/>
@@ -3730,8 +3695,7 @@
         <v>0.4805362688</v>
       </c>
       <c r="S28" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0037029420697934</v>
       </c>
       <c r="T28" s="15">
         <v>0.29178906058417492</v>
@@ -3741,8 +3705,7 @@
         <v>1</v>
       </c>
       <c r="W28" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185389.81177757643</v>
       </c>
       <c r="X28" s="16"/>
       <c r="Y28" s="17"/>
@@ -3808,8 +3771,7 @@
         <v>0.4805362688</v>
       </c>
       <c r="S29" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.005839858184344</v>
       </c>
       <c r="T29" s="15">
         <v>0.29178906058417492</v>
@@ -3819,8 +3781,7 @@
         <v>1</v>
       </c>
       <c r="W29" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185819.13889795271</v>
       </c>
       <c r="X29" s="16"/>
       <c r="Y29" s="17"/>
@@ -3886,8 +3847,7 @@
         <v>1.0665561088</v>
       </c>
       <c r="S30" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.991197014867232</v>
       </c>
       <c r="T30" s="15">
         <v>0.64706360715319111</v>
@@ -3897,8 +3857,7 @@
         <v>1</v>
       </c>
       <c r="W30" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185104.93514622728</v>
       </c>
       <c r="X30" s="16"/>
       <c r="Y30" s="17"/>
@@ -3964,8 +3923,7 @@
         <v>1.0665561088</v>
       </c>
       <c r="S31" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0061597799357331</v>
       </c>
       <c r="T31" s="15">
         <v>0.64706360715319111</v>
@@ -3975,8 +3933,7 @@
         <v>1</v>
       </c>
       <c r="W31" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185608.40075927755</v>
       </c>
       <c r="X31" s="16"/>
       <c r="Y31" s="17"/>
@@ -4042,8 +3999,7 @@
         <v>1.0665561088</v>
       </c>
       <c r="S32" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.993572661817522</v>
       </c>
       <c r="T32" s="15">
         <v>0.64706360715319111</v>
@@ -4053,8 +4009,7 @@
         <v>1</v>
       </c>
       <c r="W32" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>186034.58674326047</v>
       </c>
       <c r="X32" s="16"/>
       <c r="Y32" s="17"/>
@@ -4120,8 +4075,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S33" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9854829420546865</v>
       </c>
       <c r="T33" s="15">
         <v>1.2294208535910629</v>
@@ -4131,8 +4085,7 @@
         <v>1</v>
       </c>
       <c r="W33" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184901.49224863882</v>
       </c>
       <c r="X33" s="16"/>
       <c r="Y33" s="17"/>
@@ -4198,8 +4151,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S34" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.997459171758833</v>
       </c>
       <c r="T34" s="15">
         <v>1.2294208535910629</v>
@@ -4209,8 +4161,7 @@
         <v>1</v>
       </c>
       <c r="W34" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185400.66534815036</v>
       </c>
       <c r="X34" s="16"/>
       <c r="Y34" s="17"/>
@@ -4276,8 +4227,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S35" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9995329179000736</v>
       </c>
       <c r="T35" s="15">
         <v>1.2294208535910629</v>
@@ -4287,8 +4237,7 @@
         <v>1</v>
       </c>
       <c r="W35" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185642.91866813597</v>
       </c>
       <c r="X35" s="16"/>
       <c r="Y35" s="17"/>
@@ -4354,8 +4303,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S36" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0024032305178814</v>
       </c>
       <c r="T36" s="15">
         <v>1.2294208535910629</v>
@@ -4365,8 +4313,7 @@
         <v>1</v>
       </c>
       <c r="W36" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184474.96034178149</v>
       </c>
       <c r="X36" s="16"/>
       <c r="Y36" s="17"/>
@@ -4432,8 +4379,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S37" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0002989469734507</v>
       </c>
       <c r="T37" s="15">
         <v>1.2294208535910629</v>
@@ -4443,8 +4389,7 @@
         <v>1</v>
       </c>
       <c r="W37" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185047.77506841425</v>
       </c>
       <c r="X37" s="16"/>
       <c r="Y37" s="17"/>
@@ -4510,8 +4455,7 @@
         <v>2.8392661248</v>
       </c>
       <c r="S38" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0051228242956798</v>
       </c>
       <c r="T38" s="15">
         <v>1.2294208535910629</v>
@@ -4521,8 +4465,7 @@
         <v>1</v>
       </c>
       <c r="W38" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184730.72246780823</v>
       </c>
       <c r="X38" s="16"/>
       <c r="Y38" s="17"/>
@@ -4588,8 +4531,7 @@
         <v>2.0246985471999999</v>
       </c>
       <c r="S39" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9917179484332892</v>
       </c>
       <c r="T39" s="15">
         <v>1.2294208535910629</v>
@@ -4599,8 +4541,7 @@
         <v>1</v>
       </c>
       <c r="W39" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184657.84894821202</v>
       </c>
       <c r="X39" s="16"/>
       <c r="Y39" s="17"/>
@@ -4666,8 +4607,7 @@
         <v>1.6672264448</v>
       </c>
       <c r="S40" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9965582613824604</v>
       </c>
       <c r="T40" s="15">
         <v>1.035301771445106</v>
@@ -4677,8 +4617,7 @@
         <v>1</v>
       </c>
       <c r="W40" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184509.38583977998</v>
       </c>
       <c r="X40" s="16"/>
       <c r="Y40" s="17"/>
@@ -4744,8 +4683,7 @@
         <v>1.6672264448</v>
       </c>
       <c r="S41" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9819584591531778</v>
       </c>
       <c r="T41" s="15">
         <v>1.035301771445106</v>
@@ -4755,8 +4693,7 @@
         <v>1</v>
       </c>
       <c r="W41" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184799.29824502673</v>
       </c>
       <c r="X41" s="16"/>
       <c r="Y41" s="17"/>
@@ -4822,8 +4759,7 @@
         <v>1.6672264448</v>
       </c>
       <c r="S42" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0106972588396674</v>
       </c>
       <c r="T42" s="15">
         <v>1.035301771445106</v>
@@ -4833,8 +4769,7 @@
         <v>1</v>
       </c>
       <c r="W42" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185809.73121126543</v>
       </c>
       <c r="X42" s="16"/>
       <c r="Y42" s="17"/>
@@ -4900,8 +4835,7 @@
         <v>1.6672264448</v>
       </c>
       <c r="S43" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.017196929862882</v>
       </c>
       <c r="T43" s="15">
         <v>1.035301771445106</v>
@@ -4911,8 +4845,7 @@
         <v>1</v>
       </c>
       <c r="W43" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185603.96631342368</v>
       </c>
       <c r="X43" s="16"/>
       <c r="Y43" s="17"/>
@@ -4978,8 +4911,7 @@
         <v>1.010884224</v>
       </c>
       <c r="S44" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0091834892806224</v>
       </c>
       <c r="T44" s="15">
         <v>0.61532086416077048</v>
@@ -4989,8 +4921,7 @@
         <v>1</v>
       </c>
       <c r="W44" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185307.91072169744</v>
       </c>
       <c r="X44" s="16"/>
       <c r="Y44" s="17"/>
@@ -5056,8 +4987,7 @@
         <v>1.010884224</v>
       </c>
       <c r="S45" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9925767191153558</v>
       </c>
       <c r="T45" s="15">
         <v>0.61532086416077048</v>
@@ -5067,8 +4997,7 @@
         <v>1</v>
       </c>
       <c r="W45" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185288.47649714549</v>
       </c>
       <c r="X45" s="16"/>
       <c r="Y45" s="17"/>
@@ -5134,8 +5063,7 @@
         <v>1.010884224</v>
       </c>
       <c r="S46" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0101119866597745</v>
       </c>
       <c r="T46" s="15">
         <v>0.61532086416077048</v>
@@ -5145,8 +5073,7 @@
         <v>1</v>
       </c>
       <c r="W46" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184995.02854247691</v>
       </c>
       <c r="X46" s="16"/>
       <c r="Y46" s="17"/>
@@ -5212,8 +5139,7 @@
         <v>1.010884224</v>
       </c>
       <c r="S47" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0098220679224212</v>
       </c>
       <c r="T47" s="15">
         <v>0.61532086416077048</v>
@@ -5223,8 +5149,7 @@
         <v>1</v>
       </c>
       <c r="W47" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185517.329574648</v>
       </c>
       <c r="X47" s="16"/>
       <c r="Y47" s="17"/>
@@ -5290,8 +5215,7 @@
         <v>2.0041878527999999</v>
       </c>
       <c r="S48" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9897531700857938</v>
       </c>
       <c r="T48" s="15">
         <v>1.215991231555809</v>
@@ -5301,8 +5225,7 @@
         <v>1</v>
       </c>
       <c r="W48" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184961.35698070243</v>
       </c>
       <c r="X48" s="16"/>
       <c r="Y48" s="17"/>
@@ -5368,8 +5291,7 @@
         <v>2.0041878527999999</v>
       </c>
       <c r="S49" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9862603838354991</v>
       </c>
       <c r="T49" s="15">
         <v>1.215991231555809</v>
@@ -5379,8 +5301,7 @@
         <v>1</v>
       </c>
       <c r="W49" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>186095.82847695384</v>
       </c>
       <c r="X49" s="16"/>
       <c r="Y49" s="17"/>
@@ -5446,8 +5367,7 @@
         <v>4.9254967552000002</v>
       </c>
       <c r="S50" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0074882750215002</v>
       </c>
       <c r="T50" s="15">
         <v>2.4270989641897058</v>
@@ -5457,8 +5377,7 @@
         <v>1</v>
       </c>
       <c r="W50" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184760.54978107175</v>
       </c>
       <c r="X50" s="16"/>
       <c r="Y50" s="17"/>
@@ -5524,8 +5443,7 @@
         <v>2.4407726336</v>
       </c>
       <c r="S51" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0036603716558323</v>
       </c>
       <c r="T51" s="15">
         <v>1.4821419227999511</v>
@@ -5535,8 +5453,7 @@
         <v>1</v>
       </c>
       <c r="W51" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184916.49235875334</v>
       </c>
       <c r="X51" s="16"/>
       <c r="Y51" s="17"/>
@@ -5602,8 +5519,7 @@
         <v>2.4407726336</v>
       </c>
       <c r="S52" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0024127806114826</v>
       </c>
       <c r="T52" s="15">
         <v>1.4821419227999511</v>
@@ -5613,8 +5529,7 @@
         <v>1</v>
       </c>
       <c r="W52" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185868.4739743674</v>
       </c>
       <c r="X52" s="16"/>
       <c r="Y52" s="17"/>
@@ -5680,8 +5595,7 @@
         <v>1.2775232512000001</v>
       </c>
       <c r="S53" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9994663314749208</v>
       </c>
       <c r="T53" s="15">
         <v>0.77647632858382953</v>
@@ -5691,8 +5605,7 @@
         <v>1</v>
       </c>
       <c r="W53" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184948.53430522149</v>
       </c>
       <c r="X53" s="16"/>
       <c r="Y53" s="17"/>
@@ -5758,8 +5671,7 @@
         <v>3.6509036032000011</v>
       </c>
       <c r="S54" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9884909016830288</v>
       </c>
       <c r="T54" s="15">
         <v>1.9411908214595739</v>
@@ -5769,8 +5681,7 @@
         <v>1</v>
       </c>
       <c r="W54" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185903.61123051611</v>
       </c>
       <c r="X54" s="16"/>
       <c r="Y54" s="17"/>
@@ -5836,8 +5747,7 @@
         <v>3.6509036032000011</v>
       </c>
       <c r="S55" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0073214324012847</v>
       </c>
       <c r="T55" s="15">
         <v>1.9411908214595739</v>
@@ -5847,8 +5757,7 @@
         <v>1</v>
       </c>
       <c r="W55" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184492.21754004052</v>
       </c>
       <c r="X55" s="16"/>
       <c r="Y55" s="17"/>
@@ -5914,8 +5823,7 @@
         <v>1.7053177343999999</v>
       </c>
       <c r="S56" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0177622807929652</v>
       </c>
       <c r="T56" s="15">
         <v>1.035301771445106</v>
@@ -5925,8 +5833,7 @@
         <v>1</v>
       </c>
       <c r="W56" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184453.49662864066</v>
       </c>
       <c r="X56" s="16"/>
       <c r="Y56" s="17"/>
@@ -5992,8 +5899,7 @@
         <v>0.95814243840000002</v>
       </c>
       <c r="S57" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9972379430292366</v>
       </c>
       <c r="T57" s="15">
         <v>0.58235724643787201</v>
@@ -6003,8 +5909,7 @@
         <v>1</v>
       </c>
       <c r="W57" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185341.86347413206</v>
       </c>
       <c r="X57" s="16"/>
       <c r="Y57" s="17"/>
@@ -6070,8 +5975,7 @@
         <v>0.95814243840000002</v>
       </c>
       <c r="S58" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0020925332308925</v>
       </c>
       <c r="T58" s="15">
         <v>0.58235724643787201</v>
@@ -6081,8 +5985,7 @@
         <v>1</v>
       </c>
       <c r="W58" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185041.66720668378</v>
       </c>
       <c r="X58" s="16"/>
       <c r="Y58" s="17"/>
@@ -6148,8 +6051,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S59" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0097703947762353</v>
       </c>
       <c r="T59" s="15">
         <v>1.9411908214595739</v>
@@ -6159,8 +6061,7 @@
         <v>1</v>
       </c>
       <c r="W59" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184691.24047270988</v>
       </c>
       <c r="X59" s="16"/>
       <c r="Y59" s="17"/>
@@ -6226,8 +6127,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S60" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.985644766431613</v>
       </c>
       <c r="T60" s="15">
         <v>1.9411908214595739</v>
@@ -6237,8 +6137,7 @@
         <v>1</v>
       </c>
       <c r="W60" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185869.1009201206</v>
       </c>
       <c r="X60" s="16"/>
       <c r="Y60" s="17"/>
@@ -6304,8 +6203,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S61" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0028695200760618</v>
       </c>
       <c r="T61" s="15">
         <v>1.9411908214595739</v>
@@ -6315,8 +6213,7 @@
         <v>1</v>
       </c>
       <c r="W61" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184612.20974017589</v>
       </c>
       <c r="X61" s="16"/>
       <c r="Y61" s="17"/>
@@ -6382,8 +6279,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S62" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.991409828622865</v>
       </c>
       <c r="T62" s="15">
         <v>1.9411908214595739</v>
@@ -6393,8 +6289,7 @@
         <v>1</v>
       </c>
       <c r="W62" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185109.91826490141</v>
       </c>
       <c r="X62" s="16"/>
       <c r="Y62" s="17"/>
@@ -6460,8 +6355,7 @@
         <v>4.9020559616000003</v>
       </c>
       <c r="S63" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9922938649690534</v>
       </c>
       <c r="T63" s="15">
         <v>2.976492592904679</v>
@@ -6471,8 +6365,7 @@
         <v>1</v>
       </c>
       <c r="W63" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185028.70917266962</v>
       </c>
       <c r="X63" s="16"/>
       <c r="Y63" s="17"/>
@@ -6538,8 +6431,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S64" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0090927820861788</v>
       </c>
       <c r="T64" s="15">
         <v>1.9411908214595739</v>
@@ -6549,8 +6441,7 @@
         <v>1</v>
       </c>
       <c r="W64" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185767.95670277631</v>
       </c>
       <c r="X64" s="16"/>
       <c r="Y64" s="17"/>
@@ -6616,8 +6507,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S65" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9929927973648609</v>
       </c>
       <c r="T65" s="15">
         <v>1.9411908214595739</v>
@@ -6627,8 +6517,7 @@
         <v>1</v>
       </c>
       <c r="W65" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185550.9856454629</v>
       </c>
       <c r="X65" s="16"/>
       <c r="Y65" s="17"/>
@@ -6694,8 +6583,7 @@
         <v>4.9020559616000003</v>
       </c>
       <c r="S66" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9888637947807375</v>
       </c>
       <c r="T66" s="15">
         <v>2.976492592904679</v>
@@ -6705,8 +6593,7 @@
         <v>1</v>
       </c>
       <c r="W66" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184595.00131926785</v>
       </c>
       <c r="X66" s="16"/>
       <c r="Y66" s="17"/>
@@ -6772,8 +6659,7 @@
         <v>3.1967382272</v>
       </c>
       <c r="S67" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0118053615094489</v>
       </c>
       <c r="T67" s="15">
         <v>1.9411908214595739</v>
@@ -6783,8 +6669,7 @@
         <v>1</v>
       </c>
       <c r="W67" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185350.03176557153</v>
       </c>
       <c r="X67" s="16"/>
       <c r="Y67" s="17"/>
@@ -6850,8 +6735,7 @@
         <v>2.0041878527999999</v>
       </c>
       <c r="S68" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.0143418170875869</v>
       </c>
       <c r="T68" s="15">
         <v>1.215991231555809</v>
@@ -6861,8 +6745,7 @@
         <v>1</v>
       </c>
       <c r="W68" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>184939.17981964117</v>
       </c>
       <c r="X68" s="16"/>
       <c r="Y68" s="17"/>
@@ -6928,8 +6811,7 @@
         <v>8.9016413696000001</v>
       </c>
       <c r="S69" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.9930482025895846</v>
       </c>
       <c r="T69" s="15">
         <v>4.8529770536489343</v>
@@ -6939,8 +6821,7 @@
         <v>1</v>
       </c>
       <c r="W69" s="15">
-        <f t="shared" si="2"/>
-        <v>185220</v>
+        <v>185532.28282785535</v>
       </c>
       <c r="X69" s="16"/>
       <c r="Y69" s="17"/>
@@ -7005,8 +6886,7 @@
         <v>92.819682457599981</v>
       </c>
       <c r="S70" s="15">
-        <f>0.005*1000</f>
-        <v>5</v>
+        <v>4.9973407017308826</v>
       </c>
       <c r="T70" s="15">
         <v>188.58660726897881</v>
@@ -7016,8 +6896,7 @@
         <v>1</v>
       </c>
       <c r="W70" s="15">
-        <f>AVERAGE(900,1300)*1000/30</f>
-        <v>36666.666666666664</v>
+        <v>36659.788730141707</v>
       </c>
       <c r="X70" s="16"/>
       <c r="Y70" s="17"/>
@@ -7082,8 +6961,7 @@
         <v>239.51802900480001</v>
       </c>
       <c r="S71" s="15">
-        <f t="shared" ref="S71:S107" si="3">0.005*1000</f>
-        <v>5</v>
+        <v>5.0206132009775208</v>
       </c>
       <c r="T71" s="15">
         <v>577.02930869636782</v>
@@ -7093,8 +6971,7 @@
         <v>1</v>
       </c>
       <c r="W71" s="15">
-        <f t="shared" ref="W71:W107" si="4">AVERAGE(900,1300)*1000/30</f>
-        <v>36666.666666666664</v>
+        <v>36486.054693197373</v>
       </c>
       <c r="X71" s="16"/>
       <c r="Y71" s="17"/>
@@ -7159,8 +7036,7 @@
         <v>382.53324085759999</v>
       </c>
       <c r="S72" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0099169323596549</v>
       </c>
       <c r="T72" s="15">
         <v>1454.160999954471</v>
@@ -7170,8 +7046,7 @@
         <v>1</v>
       </c>
       <c r="W72" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36602.424577377657</v>
       </c>
       <c r="X72" s="16"/>
       <c r="Y72" s="17"/>
@@ -7236,8 +7111,7 @@
         <v>188.56067381759999</v>
       </c>
       <c r="S73" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0241799275947008</v>
       </c>
       <c r="T73" s="15">
         <v>454.42527857258767</v>
@@ -7247,8 +7121,7 @@
         <v>1</v>
       </c>
       <c r="W73" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36839.016970626035</v>
       </c>
       <c r="X73" s="16"/>
       <c r="Y73" s="17"/>
@@ -7313,8 +7186,7 @@
         <v>11.398085888000001</v>
       </c>
       <c r="S74" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9851390420569777</v>
       </c>
       <c r="T74" s="15">
         <v>61.34759438196869</v>
@@ -7324,8 +7196,7 @@
         <v>1</v>
       </c>
       <c r="W74" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36507.263768175035</v>
       </c>
       <c r="X74" s="16"/>
       <c r="Y74" s="17"/>
@@ -7390,8 +7261,7 @@
         <v>148.18390684159999</v>
       </c>
       <c r="S75" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.023185883706816</v>
       </c>
       <c r="T75" s="15">
         <v>250.38836701887351</v>
@@ -7401,8 +7271,7 @@
         <v>1</v>
       </c>
       <c r="W75" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36783.982343859592</v>
       </c>
       <c r="X75" s="16"/>
       <c r="Y75" s="17"/>
@@ -7467,8 +7336,7 @@
         <v>18.9665321216</v>
       </c>
       <c r="S76" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0212514407357931</v>
       </c>
       <c r="T76" s="15">
         <v>64.982545158236235</v>
@@ -7478,8 +7346,7 @@
         <v>1</v>
       </c>
       <c r="W76" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X76" s="16"/>
       <c r="Y76" s="17"/>
@@ -7544,8 +7411,7 @@
         <v>43.766891750399999</v>
       </c>
       <c r="S77" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9995257325797899</v>
       </c>
       <c r="T77" s="15">
         <v>149.9603039461872</v>
@@ -7555,8 +7421,7 @@
         <v>1</v>
       </c>
       <c r="W77" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36687.155716645873</v>
       </c>
       <c r="X77" s="16"/>
       <c r="Y77" s="17"/>
@@ -7621,8 +7486,7 @@
         <v>60.575405811200007</v>
       </c>
       <c r="S78" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.989760959169903</v>
       </c>
       <c r="T78" s="15">
         <v>324.95955246531918</v>
@@ -7632,8 +7496,7 @@
         <v>1</v>
       </c>
       <c r="W78" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36709.985756943868</v>
       </c>
       <c r="X78" s="16"/>
       <c r="Y78" s="17"/>
@@ -7698,8 +7561,7 @@
         <v>764.83500387840002</v>
       </c>
       <c r="S79" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0244020823608571</v>
       </c>
       <c r="T79" s="15">
         <v>2710.1924938039851</v>
@@ -7709,8 +7571,7 @@
         <v>1</v>
       </c>
       <c r="W79" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36794.091213806954</v>
       </c>
       <c r="X79" s="16"/>
       <c r="Y79" s="17"/>
@@ -7775,8 +7636,7 @@
         <v>227.60131555839999</v>
       </c>
       <c r="S80" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9845856109496776</v>
       </c>
       <c r="T80" s="15">
         <v>681.63764655340492</v>
@@ -7786,8 +7646,7 @@
         <v>1</v>
       </c>
       <c r="W80" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36789.449598837331</v>
       </c>
       <c r="X80" s="16"/>
       <c r="Y80" s="17"/>
@@ -7852,8 +7711,7 @@
         <v>128.15667880960001</v>
       </c>
       <c r="S81" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0024651299793081</v>
       </c>
       <c r="T81" s="15">
         <v>260.38543122277753</v>
@@ -7863,8 +7721,7 @@
         <v>1</v>
       </c>
       <c r="W81" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36829.005134729479</v>
       </c>
       <c r="X81" s="16"/>
       <c r="Y81" s="17"/>
@@ -7929,8 +7786,7 @@
         <v>200.316231808</v>
       </c>
       <c r="S82" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.014399595204905</v>
       </c>
       <c r="T82" s="15">
         <v>748.66583500564445</v>
@@ -7940,8 +7796,7 @@
         <v>1</v>
       </c>
       <c r="W82" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36631.917892017293</v>
       </c>
       <c r="X82" s="16"/>
       <c r="Y82" s="17"/>
@@ -8006,8 +7861,7 @@
         <v>36.749304166400002</v>
       </c>
       <c r="S83" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9949347931217094</v>
       </c>
       <c r="T83" s="15">
         <v>122.69464615298411</v>
@@ -8017,8 +7871,7 @@
         <v>1</v>
       </c>
       <c r="W83" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36687.517502362512</v>
       </c>
       <c r="X83" s="16"/>
       <c r="Y83" s="17"/>
@@ -8083,8 +7936,7 @@
         <v>1125.4921241088</v>
       </c>
       <c r="S84" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0135718911613969</v>
       </c>
       <c r="T84" s="15">
         <v>4287.5023052793667</v>
@@ -8094,8 +7946,7 @@
         <v>1</v>
       </c>
       <c r="W84" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36576.430336444217</v>
       </c>
       <c r="X84" s="16"/>
       <c r="Y84" s="17"/>
@@ -8160,8 +8011,7 @@
         <v>213.6599035648</v>
       </c>
       <c r="S85" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0117768555004183</v>
       </c>
       <c r="T85" s="15">
         <v>701.63286018311953</v>
@@ -8171,8 +8021,7 @@
         <v>1</v>
       </c>
       <c r="W85" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36547.992678641953</v>
       </c>
       <c r="X85" s="16"/>
       <c r="Y85" s="17"/>
@@ -8237,8 +8086,7 @@
         <v>691.41550822399995</v>
       </c>
       <c r="S86" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0007761009507812</v>
       </c>
       <c r="T86" s="15">
         <v>2812.8924689382079</v>
@@ -8248,8 +8096,7 @@
         <v>1</v>
       </c>
       <c r="W86" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36809.002404996965</v>
       </c>
       <c r="X86" s="16"/>
       <c r="Y86" s="17"/>
@@ -8314,8 +8161,7 @@
         <v>145.8925692672</v>
       </c>
       <c r="S87" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0191542938752622</v>
       </c>
       <c r="T87" s="15">
         <v>636.19560704600406</v>
@@ -8325,8 +8171,7 @@
         <v>1</v>
       </c>
       <c r="W87" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36743.907710513122</v>
       </c>
       <c r="X87" s="16"/>
       <c r="Y87" s="17"/>
@@ -8391,8 +8236,7 @@
         <v>114.5405078272</v>
       </c>
       <c r="S88" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0095416335835186</v>
       </c>
       <c r="T88" s="15">
         <v>117.2419486831061</v>
@@ -8402,8 +8246,7 @@
         <v>1</v>
       </c>
       <c r="W88" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36503.403432982275</v>
       </c>
       <c r="X88" s="16"/>
       <c r="Y88" s="17"/>
@@ -8468,8 +8311,7 @@
         <v>243.9483389952</v>
       </c>
       <c r="S89" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0117662805804128</v>
       </c>
       <c r="T89" s="15">
         <v>1431.439708895294</v>
@@ -8479,8 +8321,7 @@
         <v>1</v>
       </c>
       <c r="W89" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36604.270577223338</v>
       </c>
       <c r="X89" s="16"/>
       <c r="Y89" s="17"/>
@@ -8545,8 +8386,7 @@
         <v>782.17533094400005</v>
       </c>
       <c r="S90" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9822609680594487</v>
       </c>
       <c r="T90" s="15">
         <v>3080.0947215675019</v>
@@ -8556,8 +8396,7 @@
         <v>1</v>
       </c>
       <c r="W90" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36510.293021424797</v>
       </c>
       <c r="X90" s="16"/>
       <c r="Y90" s="17"/>
@@ -8622,8 +8461,7 @@
         <v>737.10161495039995</v>
       </c>
       <c r="S91" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0081176192462102</v>
       </c>
       <c r="T91" s="15">
         <v>2890.144532972839</v>
@@ -8633,8 +8471,7 @@
         <v>1</v>
       </c>
       <c r="W91" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36661.979776206987</v>
       </c>
       <c r="X91" s="16"/>
       <c r="Y91" s="17"/>
@@ -8699,8 +8536,7 @@
         <v>708.7909964800001</v>
       </c>
       <c r="S92" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0184057428618996</v>
       </c>
       <c r="T92" s="15">
         <v>3055.100975835835</v>
@@ -8710,8 +8546,7 @@
         <v>1</v>
       </c>
       <c r="W92" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36766.652708199232</v>
       </c>
       <c r="X92" s="16"/>
       <c r="Y92" s="17"/>
@@ -8776,8 +8611,7 @@
         <v>72.66646016</v>
       </c>
       <c r="S93" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.008358071687625</v>
       </c>
       <c r="T93" s="15">
         <v>147.64281256457221</v>
@@ -8787,8 +8621,7 @@
         <v>1</v>
       </c>
       <c r="W93" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36814.588149643198</v>
       </c>
       <c r="X93" s="16"/>
       <c r="Y93" s="17"/>
@@ -8853,8 +8686,7 @@
         <v>552.73391308800001</v>
       </c>
       <c r="S94" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0090770917326255</v>
       </c>
       <c r="T94" s="15">
         <v>2976.485873086473</v>
@@ -8864,8 +8696,7 @@
         <v>1</v>
       </c>
       <c r="W94" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36575.41371462668</v>
       </c>
       <c r="X94" s="16"/>
       <c r="Y94" s="17"/>
@@ -8930,8 +8761,7 @@
         <v>77.161232332799983</v>
       </c>
       <c r="S95" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9849685880043655</v>
       </c>
       <c r="T95" s="15">
         <v>156.77658274174959</v>
@@ -8941,8 +8771,7 @@
         <v>1</v>
       </c>
       <c r="W95" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36818.603691801472</v>
       </c>
       <c r="X95" s="16"/>
       <c r="Y95" s="17"/>
@@ -9007,8 +8836,7 @@
         <v>258.51520996403201</v>
       </c>
       <c r="S96" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9992867727898362</v>
       </c>
       <c r="T96" s="15">
         <v>824.78168418408154</v>
@@ -9018,8 +8846,7 @@
         <v>1</v>
       </c>
       <c r="W96" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36494.72724202049</v>
       </c>
       <c r="X96" s="16"/>
       <c r="Y96" s="17"/>
@@ -9084,8 +8911,7 @@
         <v>111.607478528</v>
       </c>
       <c r="S97" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0249808421739006</v>
       </c>
       <c r="T97" s="15">
         <v>226.75820261289121</v>
@@ -9095,8 +8921,7 @@
         <v>1</v>
       </c>
       <c r="W97" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36706.343456364113</v>
       </c>
       <c r="X97" s="16"/>
       <c r="Y97" s="17"/>
@@ -9161,8 +8986,7 @@
         <v>430.93554954240011</v>
       </c>
       <c r="S98" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.007870796904581</v>
       </c>
       <c r="T98" s="15">
         <v>1529.141151927565</v>
@@ -9172,8 +8996,7 @@
         <v>1</v>
       </c>
       <c r="W98" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36695.473173319871</v>
       </c>
       <c r="X98" s="16"/>
       <c r="Y98" s="17"/>
@@ -9238,8 +9061,7 @@
         <v>178.88548625920001</v>
       </c>
       <c r="S99" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9945393512195499</v>
       </c>
       <c r="T99" s="15">
         <v>175.18086105634029</v>
@@ -9249,8 +9071,7 @@
         <v>1</v>
       </c>
       <c r="W99" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36834.604338562982</v>
       </c>
       <c r="X99" s="16"/>
       <c r="Y99" s="17"/>
@@ -9315,8 +9136,7 @@
         <v>21.005881164800002</v>
       </c>
       <c r="S100" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0014397493941569</v>
       </c>
       <c r="T100" s="15">
         <v>113.0611312878021</v>
@@ -9326,8 +9146,7 @@
         <v>1</v>
       </c>
       <c r="W100" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36630.363391660023</v>
       </c>
       <c r="X100" s="16"/>
       <c r="Y100" s="17"/>
@@ -9392,8 +9211,7 @@
         <v>744.0049286656</v>
       </c>
       <c r="S101" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9852316935162353</v>
       </c>
       <c r="T101" s="15">
         <v>3127.809215747392</v>
@@ -9403,8 +9221,7 @@
         <v>1</v>
       </c>
       <c r="W101" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36488.230089788049</v>
       </c>
       <c r="X101" s="16"/>
       <c r="Y101" s="17"/>
@@ -9469,8 +9286,7 @@
         <v>669.93202088960004</v>
       </c>
       <c r="S102" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9954541897198155</v>
       </c>
       <c r="T102" s="15">
         <v>2703.8303803763488</v>
@@ -9480,8 +9296,7 @@
         <v>1</v>
       </c>
       <c r="W102" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36772.77602247263</v>
       </c>
       <c r="X102" s="16"/>
       <c r="Y102" s="17"/>
@@ -9546,8 +9361,7 @@
         <v>825.76348664320005</v>
       </c>
       <c r="S103" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9943286360169026</v>
       </c>
       <c r="T103" s="15">
         <v>3035.561012795953</v>
@@ -9557,8 +9371,7 @@
         <v>1</v>
       </c>
       <c r="W103" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36755.963045804827</v>
       </c>
       <c r="X103" s="16"/>
       <c r="Y103" s="17"/>
@@ -9623,8 +9436,7 @@
         <v>656.74950458879994</v>
       </c>
       <c r="S104" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9879190003772811</v>
       </c>
       <c r="T104" s="15">
         <v>2890.144532972839</v>
@@ -9634,8 +9446,7 @@
         <v>1</v>
       </c>
       <c r="W104" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36498.167789499494</v>
       </c>
       <c r="X104" s="16"/>
       <c r="Y104" s="17"/>
@@ -9700,8 +9511,7 @@
         <v>98.345849548800004</v>
       </c>
       <c r="S105" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0233885476548368</v>
       </c>
       <c r="T105" s="15">
         <v>446.24541845134081</v>
@@ -9711,8 +9521,7 @@
         <v>1</v>
       </c>
       <c r="W105" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36689.870880437578</v>
       </c>
       <c r="X105" s="16"/>
       <c r="Y105" s="17"/>
@@ -9777,8 +9586,7 @@
         <v>624.72938053120004</v>
       </c>
       <c r="S106" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.9920356617957111</v>
       </c>
       <c r="T106" s="15">
         <v>1122.4303675348681</v>
@@ -9788,8 +9596,7 @@
         <v>1</v>
       </c>
       <c r="W106" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36579.53839591991</v>
       </c>
       <c r="X106" s="16"/>
       <c r="Y106" s="17"/>
@@ -9854,8 +9661,7 @@
         <v>284.52435271680002</v>
       </c>
       <c r="S107" s="15">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.0106989655455081</v>
       </c>
       <c r="T107" s="15">
         <v>3408.189860599884</v>
@@ -9865,8 +9671,7 @@
         <v>1</v>
       </c>
       <c r="W107" s="15">
-        <f t="shared" si="4"/>
-        <v>36666.666666666664</v>
+        <v>36511.59994963825</v>
       </c>
       <c r="X107" s="16"/>
       <c r="Y107" s="17"/>
@@ -9931,8 +9736,7 @@
         <v>38.999620352000001</v>
       </c>
       <c r="S108" s="15">
-        <f>0.004*1000</f>
-        <v>4</v>
+        <v>3.9829891624255511</v>
       </c>
       <c r="T108" s="15">
         <v>46.754072792520191</v>
@@ -9942,8 +9746,7 @@
         <v>1</v>
       </c>
       <c r="W108" s="15">
-        <f>AVERAGE(450,700)*1000/30</f>
-        <v>19166.666666666668</v>
+        <v>19259.479055305928</v>
       </c>
       <c r="X108" s="16"/>
       <c r="Y108" s="17"/>
@@ -10008,8 +9811,7 @@
         <v>38.958598963199996</v>
       </c>
       <c r="S109" s="15">
-        <f t="shared" ref="S109:S172" si="5">0.004*1000</f>
-        <v>4</v>
+        <v>3.9804109525116811</v>
       </c>
       <c r="T109" s="15">
         <v>46.754072792520191</v>
@@ -10019,8 +9821,7 @@
         <v>1</v>
       </c>
       <c r="W109" s="15">
-        <f t="shared" ref="W109:W172" si="6">AVERAGE(450,700)*1000/30</f>
-        <v>19166.666666666668</v>
+        <v>19126.902621032594</v>
       </c>
       <c r="X109" s="16"/>
       <c r="Y109" s="17"/>
@@ -10085,8 +9886,7 @@
         <v>38.003386624000001</v>
       </c>
       <c r="S110" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0067381975924627</v>
       </c>
       <c r="T110" s="15">
         <v>45.557615640457207</v>
@@ -10096,8 +9896,7 @@
         <v>1</v>
       </c>
       <c r="W110" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19217.873020967818</v>
       </c>
       <c r="X110" s="16"/>
       <c r="Y110" s="17"/>
@@ -10162,8 +9961,7 @@
         <v>38.003386624000001</v>
       </c>
       <c r="S111" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0025924773917172</v>
       </c>
       <c r="T111" s="15">
         <v>45.557615640457207</v>
@@ -10173,8 +9971,7 @@
         <v>1</v>
       </c>
       <c r="W111" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19227.878982677921</v>
       </c>
       <c r="X111" s="16"/>
       <c r="Y111" s="17"/>
@@ -10239,8 +10036,7 @@
         <v>74.497772160000011</v>
       </c>
       <c r="S112" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9849371384372851</v>
       </c>
       <c r="T112" s="15">
         <v>91.851554344564974</v>
@@ -10250,8 +10046,7 @@
         <v>1</v>
       </c>
       <c r="W112" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19250.231133878537</v>
       </c>
       <c r="X112" s="16"/>
       <c r="Y112" s="17"/>
@@ -10316,8 +10111,7 @@
         <v>74.497772160000011</v>
       </c>
       <c r="S113" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0063124398557299</v>
       </c>
       <c r="T113" s="15">
         <v>91.851554344564974</v>
@@ -10327,8 +10121,7 @@
         <v>1</v>
       </c>
       <c r="W113" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19260.025664667988</v>
       </c>
       <c r="X113" s="16"/>
       <c r="Y113" s="17"/>
@@ -10393,8 +10186,7 @@
         <v>74.497772160000011</v>
       </c>
       <c r="S114" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9801972572877005</v>
       </c>
       <c r="T114" s="15">
         <v>91.851554344564974</v>
@@ -10404,8 +10196,7 @@
         <v>1</v>
       </c>
       <c r="W114" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19196.119515368886</v>
       </c>
       <c r="X114" s="16"/>
       <c r="Y114" s="17"/>
@@ -10470,8 +10261,7 @@
         <v>71.195550361599999</v>
       </c>
       <c r="S115" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0146230630762272</v>
       </c>
       <c r="T115" s="15">
         <v>92.035499457739277</v>
@@ -10481,8 +10271,7 @@
         <v>1</v>
       </c>
       <c r="W115" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19164.24915502602</v>
       </c>
       <c r="X115" s="16"/>
       <c r="Y115" s="17"/>
@@ -10547,8 +10336,7 @@
         <v>75.010539520000009</v>
       </c>
       <c r="S116" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0195681368718361</v>
       </c>
       <c r="T116" s="15">
         <v>92.035499457739277</v>
@@ -10558,8 +10346,7 @@
         <v>1</v>
       </c>
       <c r="W116" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19124.541011868296</v>
       </c>
       <c r="X116" s="16"/>
       <c r="Y116" s="17"/>
@@ -10624,8 +10411,7 @@
         <v>75.010539520000009</v>
       </c>
       <c r="S117" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9889249260953816</v>
       </c>
       <c r="T117" s="15">
         <v>92.035499457739277</v>
@@ -10635,8 +10421,7 @@
         <v>1</v>
       </c>
       <c r="W117" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19205.936895543888</v>
       </c>
       <c r="X117" s="16"/>
       <c r="Y117" s="17"/>
@@ -10701,8 +10486,7 @@
         <v>75.010539520000009</v>
       </c>
       <c r="S118" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0191417373394378</v>
       </c>
       <c r="T118" s="15">
         <v>92.035499457739277</v>
@@ -10712,8 +10496,7 @@
         <v>1</v>
       </c>
       <c r="W118" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19087.855242866568</v>
       </c>
       <c r="X118" s="16"/>
       <c r="Y118" s="17"/>
@@ -10778,8 +10561,7 @@
         <v>75.010539520000009</v>
       </c>
       <c r="S119" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0084526834710204</v>
       </c>
       <c r="T119" s="15">
         <v>92.035499457739277</v>
@@ -10789,8 +10571,7 @@
         <v>1</v>
       </c>
       <c r="W119" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19222.025052743295</v>
       </c>
       <c r="X119" s="16"/>
       <c r="Y119" s="17"/>
@@ -10855,8 +10636,7 @@
         <v>30.7572513024</v>
       </c>
       <c r="S120" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0162863380111169</v>
       </c>
       <c r="T120" s="15">
         <v>39.759274993316588</v>
@@ -10866,8 +10646,7 @@
         <v>1</v>
       </c>
       <c r="W120" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19259.836526673469</v>
       </c>
       <c r="X120" s="16"/>
       <c r="Y120" s="17"/>
@@ -10932,8 +10711,7 @@
         <v>30.7572513024</v>
       </c>
       <c r="S121" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9925017460203547</v>
       </c>
       <c r="T121" s="15">
         <v>39.759274993316588</v>
@@ -10943,8 +10721,7 @@
         <v>1</v>
       </c>
       <c r="W121" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19128.194281051306</v>
       </c>
       <c r="X121" s="16"/>
       <c r="Y121" s="17"/>
@@ -11009,8 +10786,7 @@
         <v>30.7572513024</v>
       </c>
       <c r="S122" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.996178515957062</v>
       </c>
       <c r="T122" s="15">
         <v>39.759274993316588</v>
@@ -11020,8 +10796,7 @@
         <v>1</v>
       </c>
       <c r="W122" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19166.729615511947</v>
       </c>
       <c r="X122" s="16"/>
       <c r="Y122" s="17"/>
@@ -11086,8 +10861,7 @@
         <v>76.61916398080001</v>
       </c>
       <c r="S123" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0065047038388819</v>
       </c>
       <c r="T123" s="15">
         <v>91.851554344564974</v>
@@ -11097,8 +10871,7 @@
         <v>1</v>
       </c>
       <c r="W123" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19137.772732922636</v>
       </c>
       <c r="X123" s="16"/>
       <c r="Y123" s="17"/>
@@ -11163,8 +10936,7 @@
         <v>5.0778619135999996</v>
       </c>
       <c r="S124" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9952253684703081</v>
       </c>
       <c r="T124" s="15">
         <v>12.700894584280389</v>
@@ -11174,8 +10946,7 @@
         <v>1</v>
       </c>
       <c r="W124" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19168.798301097657</v>
       </c>
       <c r="X124" s="16"/>
       <c r="Y124" s="17"/>
@@ -11240,8 +11011,7 @@
         <v>2.8685671168</v>
       </c>
       <c r="S125" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0037933830829662</v>
       </c>
       <c r="T125" s="15">
         <v>7.1787429123779054</v>
@@ -11251,8 +11021,7 @@
         <v>1</v>
       </c>
       <c r="W125" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19092.401216736529</v>
       </c>
       <c r="X125" s="16"/>
       <c r="Y125" s="17"/>
@@ -11317,8 +11086,7 @@
         <v>2.8685671168</v>
       </c>
       <c r="S126" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0124317128289375</v>
       </c>
       <c r="T126" s="15">
         <v>7.1787429123779054</v>
@@ -11328,8 +11096,7 @@
         <v>1</v>
       </c>
       <c r="W126" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19142.992895931984</v>
       </c>
       <c r="X126" s="16"/>
       <c r="Y126" s="17"/>
@@ -11394,8 +11161,7 @@
         <v>5.0778619135999996</v>
       </c>
       <c r="S127" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0077827744685202</v>
       </c>
       <c r="T127" s="15">
         <v>12.700894584280389</v>
@@ -11405,8 +11171,7 @@
         <v>1</v>
       </c>
       <c r="W127" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19075.018262903526</v>
       </c>
       <c r="X127" s="16"/>
       <c r="Y127" s="17"/>
@@ -11471,8 +11236,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S128" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9848168870059295</v>
       </c>
       <c r="T128" s="15">
         <v>184.07100260523299</v>
@@ -11482,8 +11246,7 @@
         <v>1</v>
       </c>
       <c r="W128" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19174.774852708342</v>
       </c>
       <c r="X128" s="16"/>
       <c r="Y128" s="17"/>
@@ -11548,8 +11311,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S129" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9812657930312061</v>
       </c>
       <c r="T129" s="15">
         <v>184.07099891547861</v>
@@ -11559,8 +11321,7 @@
         <v>1</v>
       </c>
       <c r="W129" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19107.467365561704</v>
       </c>
       <c r="X129" s="16"/>
       <c r="Y129" s="17"/>
@@ -11625,8 +11386,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S130" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9898951290924636</v>
       </c>
       <c r="T130" s="15">
         <v>184.07099891547861</v>
@@ -11636,8 +11396,7 @@
         <v>1</v>
       </c>
       <c r="W130" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19197.522858858829</v>
       </c>
       <c r="X130" s="16"/>
       <c r="Y130" s="17"/>
@@ -11702,8 +11461,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S131" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9824255760845708</v>
       </c>
       <c r="T131" s="15">
         <v>184.07099891547861</v>
@@ -11713,8 +11471,7 @@
         <v>1</v>
       </c>
       <c r="W131" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19247.572049929739</v>
       </c>
       <c r="X131" s="16"/>
       <c r="Y131" s="17"/>
@@ -11779,8 +11536,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S132" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9944765104484685</v>
       </c>
       <c r="T132" s="15">
         <v>184.07099891547861</v>
@@ -11790,8 +11546,7 @@
         <v>1</v>
       </c>
       <c r="W132" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19254.816877695837</v>
       </c>
       <c r="X132" s="16"/>
       <c r="Y132" s="17"/>
@@ -11856,8 +11611,7 @@
         <v>176.4476437248</v>
       </c>
       <c r="S133" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9843812186348422</v>
       </c>
       <c r="T133" s="15">
         <v>184.07099891547861</v>
@@ -11867,8 +11621,7 @@
         <v>1</v>
       </c>
       <c r="W133" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19115.72023110904</v>
       </c>
       <c r="X133" s="16"/>
       <c r="Y133" s="17"/>
@@ -11933,8 +11686,7 @@
         <v>0.77354618880000003</v>
       </c>
       <c r="S134" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9999791721444953</v>
       </c>
       <c r="T134" s="15">
         <v>1.932780215713537</v>
@@ -11944,8 +11696,7 @@
         <v>1</v>
       </c>
       <c r="W134" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19177.97545019157</v>
       </c>
       <c r="X134" s="16"/>
       <c r="Y134" s="17"/>
@@ -12010,8 +11761,7 @@
         <v>67.550506956800007</v>
       </c>
       <c r="S135" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0061408598067043</v>
       </c>
       <c r="T135" s="15">
         <v>81.028093658759815</v>
@@ -12021,8 +11771,7 @@
         <v>1</v>
       </c>
       <c r="W135" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19141.165138356617</v>
       </c>
       <c r="X135" s="16"/>
       <c r="Y135" s="17"/>
@@ -12087,8 +11836,7 @@
         <v>0.44244497919999998</v>
       </c>
       <c r="S136" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9863998088257167</v>
       </c>
       <c r="T136" s="15">
         <v>1.104213289999171</v>
@@ -12098,8 +11846,7 @@
         <v>1</v>
       </c>
       <c r="W136" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19199.797213765749</v>
       </c>
       <c r="X136" s="16"/>
       <c r="Y136" s="17"/>
@@ -12164,8 +11911,7 @@
         <v>24.498559411199999</v>
       </c>
       <c r="S137" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9924039463702861</v>
       </c>
       <c r="T137" s="15">
         <v>33.132910031414937</v>
@@ -12175,8 +11921,7 @@
         <v>1</v>
       </c>
       <c r="W137" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19197.008337011284</v>
       </c>
       <c r="X137" s="16"/>
       <c r="Y137" s="17"/>
@@ -12241,8 +11986,7 @@
         <v>1.1339483904000001</v>
       </c>
       <c r="S138" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0167815900343884</v>
       </c>
       <c r="T138" s="15">
         <v>2.8345996201256369</v>
@@ -12252,8 +11996,7 @@
         <v>1</v>
       </c>
       <c r="W138" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19249.732343363568</v>
       </c>
       <c r="X138" s="16"/>
       <c r="Y138" s="17"/>
@@ -12318,8 +12061,7 @@
         <v>1.1778998784000001</v>
       </c>
       <c r="S139" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9849142804352478</v>
       </c>
       <c r="T139" s="15">
         <v>2.945292254602212</v>
@@ -12329,8 +12071,7 @@
         <v>1</v>
       </c>
       <c r="W139" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19077.274160994268</v>
       </c>
       <c r="X139" s="16"/>
       <c r="Y139" s="17"/>
@@ -12395,8 +12136,7 @@
         <v>0.95521233919999993</v>
       </c>
       <c r="S140" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0074238509135123</v>
       </c>
       <c r="T140" s="15">
         <v>2.3929143041259682</v>
@@ -12406,8 +12146,7 @@
         <v>1</v>
       </c>
       <c r="W140" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19093.703253247237</v>
       </c>
       <c r="X140" s="16"/>
       <c r="Y140" s="17"/>
@@ -12472,8 +12211,7 @@
         <v>156.84234997760001</v>
       </c>
       <c r="S141" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9936855405363358</v>
       </c>
       <c r="T141" s="15">
         <v>592.4785277591966</v>
@@ -12483,8 +12221,7 @@
         <v>1</v>
       </c>
       <c r="W141" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19228.755469615891</v>
       </c>
       <c r="X141" s="16"/>
       <c r="Y141" s="17"/>
@@ -12549,8 +12286,7 @@
         <v>156.84234997760001</v>
       </c>
       <c r="S142" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0052229544724396</v>
       </c>
       <c r="T142" s="15">
         <v>592.4785277591966</v>
@@ -12560,8 +12296,7 @@
         <v>1</v>
       </c>
       <c r="W142" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19223.490971839743</v>
       </c>
       <c r="X142" s="16"/>
       <c r="Y142" s="17"/>
@@ -12626,8 +12361,7 @@
         <v>156.84234997760001</v>
       </c>
       <c r="S143" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0126464414149652</v>
       </c>
       <c r="T143" s="15">
         <v>592.4785277591966</v>
@@ -12637,8 +12371,7 @@
         <v>1</v>
       </c>
       <c r="W143" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19141.646787779333</v>
       </c>
       <c r="X143" s="16"/>
       <c r="Y143" s="17"/>
@@ -12703,8 +12436,7 @@
         <v>0.95521233919999993</v>
       </c>
       <c r="S144" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9972814685219635</v>
       </c>
       <c r="T144" s="15">
         <v>2.3929143041259682</v>
@@ -12714,8 +12446,7 @@
         <v>1</v>
       </c>
       <c r="W144" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19254.410070083261</v>
       </c>
       <c r="X144" s="16"/>
       <c r="Y144" s="17"/>
@@ -12780,8 +12511,7 @@
         <v>6.9912166912</v>
       </c>
       <c r="S145" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0170661418668816</v>
       </c>
       <c r="T145" s="15">
         <v>17.486723192532331</v>
@@ -12791,8 +12521,7 @@
         <v>1</v>
       </c>
       <c r="W145" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19230.607672766164</v>
       </c>
       <c r="X145" s="16"/>
       <c r="Y145" s="17"/>
@@ -12857,8 +12586,7 @@
         <v>0.95521233919999993</v>
       </c>
       <c r="S146" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9951308661634228</v>
       </c>
       <c r="T146" s="15">
         <v>2.3929143041259682</v>
@@ -12868,8 +12596,7 @@
         <v>1</v>
       </c>
       <c r="W146" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19073.646788690428</v>
       </c>
       <c r="X146" s="16"/>
       <c r="Y146" s="17"/>
@@ -12934,8 +12661,7 @@
         <v>2.2796171776</v>
       </c>
       <c r="S147" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9969903323371025</v>
       </c>
       <c r="T147" s="15">
         <v>5.7060967850767979</v>
@@ -12945,8 +12671,7 @@
         <v>1</v>
       </c>
       <c r="W147" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19251.567317422789</v>
       </c>
       <c r="X147" s="16"/>
       <c r="Y147" s="17"/>
@@ -13011,8 +12736,7 @@
         <v>51.124370841599998</v>
       </c>
       <c r="S148" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0098469625202835</v>
       </c>
       <c r="T148" s="15">
         <v>99.39818748329148</v>
@@ -13022,8 +12746,7 @@
         <v>1</v>
       </c>
       <c r="W148" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19119.074906361388</v>
       </c>
       <c r="X148" s="16"/>
       <c r="Y148" s="17"/>
@@ -13088,8 +12811,7 @@
         <v>72.103881113600011</v>
       </c>
       <c r="S149" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9841577590028217</v>
       </c>
       <c r="T149" s="15">
         <v>151.67441194771419</v>
@@ -13099,8 +12821,7 @@
         <v>1</v>
       </c>
       <c r="W149" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19119.21347169231</v>
       </c>
       <c r="X149" s="16"/>
       <c r="Y149" s="17"/>
@@ -13165,8 +12886,7 @@
         <v>45.475139583999997</v>
       </c>
       <c r="S150" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0190785798606843</v>
       </c>
       <c r="T150" s="15">
         <v>46.017749728869639</v>
@@ -13176,8 +12896,7 @@
         <v>1</v>
       </c>
       <c r="W150" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19140.576276869462</v>
       </c>
       <c r="X150" s="16"/>
       <c r="Y150" s="17"/>
@@ -13242,8 +12961,7 @@
         <v>92.667317299200008</v>
       </c>
       <c r="S151" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0040115841427513</v>
       </c>
       <c r="T151" s="15">
         <v>111.0871126396365</v>
@@ -13253,8 +12971,7 @@
         <v>1</v>
       </c>
       <c r="W151" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19071.437586680026</v>
       </c>
       <c r="X151" s="16"/>
       <c r="Y151" s="17"/>
@@ -13319,8 +13036,7 @@
         <v>92.667317299200008</v>
       </c>
       <c r="S152" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9825919625302633</v>
       </c>
       <c r="T152" s="15">
         <v>111.0871126396365</v>
@@ -13330,8 +13046,7 @@
         <v>1</v>
       </c>
       <c r="W152" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19086.139185803797</v>
       </c>
       <c r="X152" s="16"/>
       <c r="Y152" s="17"/>
@@ -13396,8 +13111,7 @@
         <v>317.60517268479998</v>
       </c>
       <c r="S153" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0062070921120476</v>
       </c>
       <c r="T153" s="15">
         <v>1066.461132922173</v>
@@ -13407,8 +13121,7 @@
         <v>1</v>
       </c>
       <c r="W153" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19210.128978306355</v>
       </c>
       <c r="X153" s="16"/>
       <c r="Y153" s="17"/>
@@ -13473,8 +13186,7 @@
         <v>317.60517268479998</v>
       </c>
       <c r="S154" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9848316690917045</v>
       </c>
       <c r="T154" s="15">
         <v>1066.461132922173</v>
@@ -13484,8 +13196,7 @@
         <v>1</v>
       </c>
       <c r="W154" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19107.723477634179</v>
       </c>
       <c r="X154" s="16"/>
       <c r="Y154" s="17"/>
@@ -13550,8 +13261,7 @@
         <v>317.60517268479998</v>
       </c>
       <c r="S155" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0047906819570844</v>
       </c>
       <c r="T155" s="15">
         <v>1066.461132922173</v>
@@ -13561,8 +13271,7 @@
         <v>1</v>
       </c>
       <c r="W155" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19255.421187046319</v>
       </c>
       <c r="X155" s="16"/>
       <c r="Y155" s="17"/>
@@ -13627,8 +13336,7 @@
         <v>317.60517268479998</v>
       </c>
       <c r="S156" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0004351462613474</v>
       </c>
       <c r="T156" s="15">
         <v>1066.461132922173</v>
@@ -13638,8 +13346,7 @@
         <v>1</v>
       </c>
       <c r="W156" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19083.958227817835</v>
       </c>
       <c r="X156" s="16"/>
       <c r="Y156" s="17"/>
@@ -13704,8 +13411,7 @@
         <v>76.381825945599999</v>
       </c>
       <c r="S157" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9857925101623835</v>
       </c>
       <c r="T157" s="15">
         <v>296.00241419847561</v>
@@ -13715,8 +13421,7 @@
         <v>1</v>
       </c>
       <c r="W157" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19220.120582362273</v>
       </c>
       <c r="X157" s="16"/>
       <c r="Y157" s="17"/>
@@ -13781,8 +13486,7 @@
         <v>23.865657983999998</v>
       </c>
       <c r="S158" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0013449509769234</v>
       </c>
       <c r="T158" s="15">
         <v>50.775362567549116</v>
@@ -13792,8 +13496,7 @@
         <v>1</v>
       </c>
       <c r="W158" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19158.314985504014</v>
       </c>
       <c r="X158" s="16"/>
       <c r="Y158" s="17"/>
@@ -13858,8 +13561,7 @@
         <v>29.8254797568</v>
       </c>
       <c r="S159" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9932738918408948</v>
       </c>
       <c r="T159" s="15">
         <v>63.454552713696849</v>
@@ -13869,8 +13571,7 @@
         <v>1</v>
       </c>
       <c r="W159" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19137.241001200535</v>
       </c>
       <c r="X159" s="16"/>
       <c r="Y159" s="17"/>
@@ -13935,8 +13636,7 @@
         <v>29.8254797568</v>
       </c>
       <c r="S160" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0136592563585598</v>
       </c>
       <c r="T160" s="15">
         <v>63.454552713696849</v>
@@ -13946,8 +13646,7 @@
         <v>1</v>
       </c>
       <c r="W160" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19093.219060293621</v>
       </c>
       <c r="X160" s="16"/>
       <c r="Y160" s="17"/>
@@ -14012,8 +13711,7 @@
         <v>76.979566182400006</v>
       </c>
       <c r="S161" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0028631768522924</v>
       </c>
       <c r="T161" s="15">
         <v>295.64700402405327</v>
@@ -14023,8 +13721,7 @@
         <v>1</v>
       </c>
       <c r="W161" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19076.31973801439</v>
       </c>
       <c r="X161" s="16"/>
       <c r="Y161" s="17"/>
@@ -14089,8 +13786,7 @@
         <v>20.246985471999999</v>
       </c>
       <c r="S162" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9822010718579572</v>
       </c>
       <c r="T162" s="15">
         <v>88.871534988950486</v>
@@ -14100,8 +13796,7 @@
         <v>1</v>
       </c>
       <c r="W162" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19120.7627287492</v>
       </c>
       <c r="X162" s="16"/>
       <c r="Y162" s="17"/>
@@ -14166,8 +13861,7 @@
         <v>71.43581849600001</v>
       </c>
       <c r="S163" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9973262336273616</v>
       </c>
       <c r="T163" s="15">
         <v>277.87215441530992</v>
@@ -14177,8 +13871,7 @@
         <v>1</v>
       </c>
       <c r="W163" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19139.187913650123</v>
       </c>
       <c r="X163" s="16"/>
       <c r="Y163" s="17"/>
@@ -14243,8 +13936,7 @@
         <v>69.097599334400002</v>
       </c>
       <c r="S164" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9972411108041612</v>
       </c>
       <c r="T164" s="15">
         <v>266.61514757780481</v>
@@ -14254,8 +13946,7 @@
         <v>1</v>
       </c>
       <c r="W164" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19192.118004613105</v>
       </c>
       <c r="X164" s="16"/>
       <c r="Y164" s="17"/>
@@ -14320,8 +14011,7 @@
         <v>69.097599334400002</v>
       </c>
       <c r="S165" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0197096514292365</v>
       </c>
       <c r="T165" s="15">
         <v>266.61514757780481</v>
@@ -14331,8 +14021,7 @@
         <v>1</v>
       </c>
       <c r="W165" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19192.728843875058</v>
       </c>
       <c r="X165" s="16"/>
       <c r="Y165" s="17"/>
@@ -14397,8 +14086,7 @@
         <v>71.6086943488</v>
       </c>
       <c r="S166" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0130336004359055</v>
       </c>
       <c r="T166" s="15">
         <v>276.68763470421982</v>
@@ -14408,8 +14096,7 @@
         <v>1</v>
       </c>
       <c r="W166" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19239.128366650282</v>
       </c>
       <c r="X166" s="16"/>
       <c r="Y166" s="17"/>
@@ -14474,8 +14161,7 @@
         <v>172.50959040000001</v>
       </c>
       <c r="S167" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0194296015229707</v>
       </c>
       <c r="T167" s="15">
         <v>293.2768793799666</v>
@@ -14485,8 +14171,7 @@
         <v>1</v>
       </c>
       <c r="W167" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19185.737749617674</v>
       </c>
       <c r="X167" s="16"/>
       <c r="Y167" s="17"/>
@@ -14551,8 +14236,7 @@
         <v>67.275077631999991</v>
       </c>
       <c r="S168" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9863348022214571</v>
       </c>
       <c r="T168" s="15">
         <v>260.80921037731781</v>
@@ -14562,8 +14246,7 @@
         <v>1</v>
       </c>
       <c r="W168" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19070.886937813877</v>
       </c>
       <c r="X168" s="16"/>
       <c r="Y168" s="17"/>
@@ -14628,8 +14311,7 @@
         <v>67.275077631999991</v>
       </c>
       <c r="S169" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9976113326493814</v>
       </c>
       <c r="T169" s="15">
         <v>260.80921037731781</v>
@@ -14639,8 +14321,7 @@
         <v>1</v>
       </c>
       <c r="W169" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19104.916937566799</v>
       </c>
       <c r="X169" s="16"/>
       <c r="Y169" s="17"/>
@@ -14705,8 +14386,7 @@
         <v>174.252999424</v>
       </c>
       <c r="S170" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0107998637908473</v>
       </c>
       <c r="T170" s="15">
         <v>296.239535185075</v>
@@ -14716,8 +14396,7 @@
         <v>1</v>
       </c>
       <c r="W170" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19241.520268120887</v>
       </c>
       <c r="X170" s="16"/>
       <c r="Y170" s="17"/>
@@ -14782,8 +14461,7 @@
         <v>174.252999424</v>
       </c>
       <c r="S171" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>4.0053319318612415</v>
       </c>
       <c r="T171" s="15">
         <v>296.239535185075</v>
@@ -14793,8 +14471,7 @@
         <v>1</v>
       </c>
       <c r="W171" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19243.799411052765</v>
       </c>
       <c r="X171" s="16"/>
       <c r="Y171" s="17"/>
@@ -14859,8 +14536,7 @@
         <v>50.008003046399999</v>
       </c>
       <c r="S172" s="15">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3.9938281996613565</v>
       </c>
       <c r="T172" s="15">
         <v>248.84084058001471</v>
@@ -14870,8 +14546,7 @@
         <v>1</v>
       </c>
       <c r="W172" s="15">
-        <f t="shared" si="6"/>
-        <v>19166.666666666668</v>
+        <v>19093.524108921647</v>
       </c>
       <c r="X172" s="16"/>
       <c r="Y172" s="17"/>
@@ -14936,8 +14611,7 @@
         <v>44.083342463999998</v>
       </c>
       <c r="S173" s="15">
-        <f t="shared" ref="S173" si="7">0.004*1000</f>
-        <v>4</v>
+        <v>3.9910660989655056</v>
       </c>
       <c r="T173" s="15">
         <v>298.60911721820833</v>
@@ -14947,8 +14621,7 @@
         <v>1</v>
       </c>
       <c r="W173" s="15">
-        <f t="shared" ref="W173" si="8">AVERAGE(450,700)*1000/30</f>
-        <v>19166.666666666668</v>
+        <v>19101.154215138049</v>
       </c>
       <c r="X173" s="16"/>
       <c r="Y173" s="17"/>
@@ -15014,7 +14687,7 @@
         <v>106.07838133760001</v>
       </c>
       <c r="S174" s="15">
-        <v>1.91</v>
+        <v>1.9133754022267866</v>
       </c>
       <c r="T174" s="15">
         <v>33.058774401298017</v>
@@ -15024,7 +14697,7 @@
         <v>1</v>
       </c>
       <c r="W174" s="15">
-        <v>40086.594535584823</v>
+        <v>40148.058375144705</v>
       </c>
       <c r="X174" s="16"/>
       <c r="Y174" s="17"/>
@@ -15080,7 +14753,7 @@
       <c r="N175" s="14"/>
       <c r="O175" s="14"/>
       <c r="P175" s="15">
-        <f t="shared" ref="P175:P178" si="9">1134.18/11.4</f>
+        <f t="shared" ref="P175:P178" si="1">1134.18/11.4</f>
         <v>99.489473684210523</v>
       </c>
       <c r="Q175" s="15">
@@ -15090,7 +14763,7 @@
         <v>106.07838133760001</v>
       </c>
       <c r="S175" s="15">
-        <v>1.91</v>
+        <v>1.9106975363151009</v>
       </c>
       <c r="T175" s="15">
         <v>33.058774401298017</v>
@@ -15100,7 +14773,7 @@
         <v>1</v>
       </c>
       <c r="W175" s="15">
-        <v>40086.594535584823</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X175" s="16"/>
       <c r="Y175" s="17"/>
@@ -15156,7 +14829,7 @@
       <c r="N176" s="14"/>
       <c r="O176" s="14"/>
       <c r="P176" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="1"/>
         <v>99.489473684210523</v>
       </c>
       <c r="Q176" s="15">
@@ -15166,7 +14839,7 @@
         <v>106.07838133760001</v>
       </c>
       <c r="S176" s="15">
-        <v>1.91</v>
+        <v>1.9123323645613817</v>
       </c>
       <c r="T176" s="15">
         <v>33.058774401298017</v>
@@ -15176,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="W176" s="15">
-        <v>40086.594535584823</v>
+        <v>39927.631087015106</v>
       </c>
       <c r="X176" s="16"/>
       <c r="Y176" s="17"/>
@@ -15232,7 +14905,7 @@
       <c r="N177" s="14"/>
       <c r="O177" s="14"/>
       <c r="P177" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="1"/>
         <v>99.489473684210523</v>
       </c>
       <c r="Q177" s="15">
@@ -15242,7 +14915,7 @@
         <v>96.910100940800007</v>
       </c>
       <c r="S177" s="15">
-        <v>1.91</v>
+        <v>1.9193048693496599</v>
       </c>
       <c r="T177" s="15">
         <v>31.594422446553089</v>
@@ -15252,7 +14925,7 @@
         <v>1</v>
       </c>
       <c r="W177" s="15">
-        <v>40086.594535584823</v>
+        <v>39909.741301349131</v>
       </c>
       <c r="X177" s="16"/>
       <c r="Y177" s="17"/>
@@ -15308,7 +14981,7 @@
       <c r="N178" s="14"/>
       <c r="O178" s="14"/>
       <c r="P178" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="1"/>
         <v>99.489473684210523</v>
       </c>
       <c r="Q178" s="15">
@@ -15318,7 +14991,7 @@
         <v>96.910100940800007</v>
       </c>
       <c r="S178" s="15">
-        <v>1.91</v>
+        <v>1.914260549816925</v>
       </c>
       <c r="T178" s="15">
         <v>31.594422446553089</v>
@@ -15328,7 +15001,7 @@
         <v>1</v>
       </c>
       <c r="W178" s="15">
-        <v>40086.594535584823</v>
+        <v>40261.304920727787</v>
       </c>
       <c r="X178" s="16"/>
       <c r="Y178" s="17"/>
@@ -15393,8 +15066,7 @@
         <v>13.246978483199999</v>
       </c>
       <c r="S179" s="15">
-        <f>0.007*1000</f>
-        <v>7</v>
+        <v>7.0042246399496237</v>
       </c>
       <c r="T179" s="15">
         <v>0</v>
@@ -15404,8 +15076,7 @@
         <v>0</v>
       </c>
       <c r="W179" s="15">
-        <f>AVERAGE(1300,1900)*1000/25</f>
-        <v>64000</v>
+        <v>64009.388115587513</v>
       </c>
       <c r="X179" s="16"/>
       <c r="Y179" s="17"/>
@@ -15470,8 +15141,7 @@
         <v>2.672250470399999</v>
       </c>
       <c r="S180" s="15">
-        <f>AVERAGE(0.004, 0.005)*1000</f>
-        <v>4.5000000000000009</v>
+        <v>4.5048006504284732</v>
       </c>
       <c r="T180" s="15">
         <v>1.8692947341755011</v>
@@ -15481,8 +15151,7 @@
         <v>1</v>
       </c>
       <c r="W180" s="15">
-        <f>AVERAGE(900,1300,450,700)*1000/30</f>
-        <v>27916.666666666668</v>
+        <v>27912.225845560282</v>
       </c>
       <c r="X180" s="16"/>
       <c r="Y180" s="17"/>
@@ -15547,8 +15216,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S181" s="15">
-        <f t="shared" ref="S181:S186" si="10">AVERAGE(0.004, 0.005)*1000</f>
-        <v>4.5000000000000009</v>
+        <v>4.4836295416574199</v>
       </c>
       <c r="T181" s="15">
         <v>2.4157039641652629</v>
@@ -15558,8 +15226,7 @@
         <v>1</v>
       </c>
       <c r="W181" s="15">
-        <f t="shared" ref="W181:W186" si="11">AVERAGE(900,1300,450,700)*1000/30</f>
-        <v>27916.666666666668</v>
+        <v>27792.435613903923</v>
       </c>
       <c r="X181" s="16"/>
       <c r="Y181" s="17"/>
@@ -15624,8 +15291,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S182" s="15">
-        <f t="shared" si="10"/>
-        <v>4.5000000000000009</v>
+        <v>4.5058030826625712</v>
       </c>
       <c r="T182" s="15">
         <v>2.4157039641652629</v>
@@ -15635,8 +15301,7 @@
         <v>1</v>
       </c>
       <c r="W182" s="15">
-        <f t="shared" si="11"/>
-        <v>27916.666666666668</v>
+        <v>27804.853098314125</v>
       </c>
       <c r="X182" s="16"/>
       <c r="Y182" s="17"/>
@@ -15701,8 +15366,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S183" s="15">
-        <f t="shared" si="10"/>
-        <v>4.5000000000000009</v>
+        <v>4.5090123255153687</v>
       </c>
       <c r="T183" s="15">
         <v>2.4157039641652629</v>
@@ -15712,8 +15376,7 @@
         <v>1</v>
       </c>
       <c r="W183" s="15">
-        <f t="shared" si="11"/>
-        <v>27916.666666666668</v>
+        <v>28029.582981907133</v>
       </c>
       <c r="X183" s="16"/>
       <c r="Y183" s="17"/>
@@ -15778,8 +15441,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S184" s="15">
-        <f t="shared" si="10"/>
-        <v>4.5000000000000009</v>
+        <v>4.5168126931637378</v>
       </c>
       <c r="T184" s="15">
         <v>2.4157039641652629</v>
@@ -15789,8 +15451,7 @@
         <v>1</v>
       </c>
       <c r="W184" s="15">
-        <f t="shared" si="11"/>
-        <v>27916.666666666668</v>
+        <v>27880.267520170946</v>
       </c>
       <c r="X184" s="16"/>
       <c r="Y184" s="17"/>
@@ -15855,8 +15516,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S185" s="15">
-        <f t="shared" si="10"/>
-        <v>4.5000000000000009</v>
+        <v>4.5081922476032483</v>
       </c>
       <c r="T185" s="15">
         <v>2.4157039641652629</v>
@@ -15866,8 +15526,7 @@
         <v>1</v>
       </c>
       <c r="W185" s="15">
-        <f t="shared" si="11"/>
-        <v>27916.666666666668</v>
+        <v>27860.124100749264</v>
       </c>
       <c r="X185" s="16"/>
       <c r="Y185" s="17"/>
@@ -15932,8 +15591,7 @@
         <v>4.6324868352000008</v>
       </c>
       <c r="S186" s="15">
-        <f t="shared" si="10"/>
-        <v>4.5000000000000009</v>
+        <v>4.5010069172596117</v>
       </c>
       <c r="T186" s="15">
         <v>2.4157039641652629</v>
@@ -15943,8 +15601,7 @@
         <v>1</v>
       </c>
       <c r="W186" s="15">
-        <f t="shared" si="11"/>
-        <v>27916.666666666668</v>
+        <v>27782.230240294346</v>
       </c>
       <c r="X186" s="16"/>
       <c r="Y186" s="17"/>
@@ -16010,8 +15667,7 @@
         <v>31.879479296</v>
       </c>
       <c r="S187" s="15">
-        <f>AVERAGE(0.005,0.005)*1000</f>
-        <v>5</v>
+        <v>5.0114912149556465</v>
       </c>
       <c r="T187" s="15">
         <v>507.34503962764381</v>
@@ -16021,8 +15677,7 @@
         <v>1</v>
       </c>
       <c r="W187" s="15">
-        <f>AVERAGE(1850,2550,1700,2300)*1000/AVERAGE(40,30)</f>
-        <v>60000</v>
+        <v>60037.830896925043</v>
       </c>
       <c r="X187" s="16"/>
       <c r="Y187" s="17"/>
@@ -16087,8 +15742,7 @@
         <v>107.28265210879999</v>
       </c>
       <c r="S188" s="15">
-        <f t="shared" ref="S188:S197" si="12">AVERAGE(0.004, 0.005)*1000</f>
-        <v>4.5000000000000009</v>
+        <v>4.49719373791977</v>
       </c>
       <c r="T188" s="15">
         <v>1380.532491866089</v>
@@ -16098,8 +15752,7 @@
         <v>1</v>
       </c>
       <c r="W188" s="15">
-        <f t="shared" ref="W188:W197" si="13">AVERAGE(900,1300,450,700)*1000/30</f>
-        <v>27916.666666666668</v>
+        <v>27964.429643597174</v>
       </c>
       <c r="X188" s="16"/>
       <c r="Y188" s="17"/>
@@ -16164,8 +15817,7 @@
         <v>168.02653862400001</v>
       </c>
       <c r="S189" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.4966261609706066</v>
       </c>
       <c r="T189" s="15">
         <v>1402.1034477042349</v>
@@ -16175,8 +15827,7 @@
         <v>1</v>
       </c>
       <c r="W189" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27969.070509919875</v>
       </c>
       <c r="X189" s="16"/>
       <c r="Y189" s="17"/>
@@ -16241,8 +15892,7 @@
         <v>352.69018050559998</v>
       </c>
       <c r="S190" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.5114298420301413</v>
       </c>
       <c r="T190" s="15">
         <v>3071.6847944020478</v>
@@ -16252,8 +15902,7 @@
         <v>1</v>
       </c>
       <c r="W190" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27919.225285296856</v>
       </c>
       <c r="X190" s="16"/>
       <c r="Y190" s="17"/>
@@ -16318,8 +15967,7 @@
         <v>101.8766190848</v>
       </c>
       <c r="S191" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.4945320024326403</v>
       </c>
       <c r="T191" s="15">
         <v>270.06669585185142</v>
@@ -16329,8 +15977,7 @@
         <v>1</v>
       </c>
       <c r="W191" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27972.463864957968</v>
       </c>
       <c r="X191" s="16"/>
       <c r="Y191" s="17"/>
@@ -16395,8 +16042,7 @@
         <v>101.8766190848</v>
       </c>
       <c r="S192" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.4812086178455415</v>
       </c>
       <c r="T192" s="15">
         <v>270.06669585185142</v>
@@ -16406,8 +16052,7 @@
         <v>1</v>
       </c>
       <c r="W192" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>28032.083272314307</v>
       </c>
       <c r="X192" s="16"/>
       <c r="Y192" s="17"/>
@@ -16472,8 +16117,7 @@
         <v>63.211030041599997</v>
       </c>
       <c r="S193" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.5079413301829474</v>
       </c>
       <c r="T193" s="15">
         <v>475.63648334868481</v>
@@ -16483,8 +16127,7 @@
         <v>1</v>
       </c>
       <c r="W193" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>28048.765875768477</v>
       </c>
       <c r="X193" s="16"/>
       <c r="Y193" s="17"/>
@@ -16549,8 +16192,7 @@
         <v>51.396870067200012</v>
       </c>
       <c r="S194" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.4818421432362205</v>
       </c>
       <c r="T194" s="15">
         <v>475.63648334868481</v>
@@ -16560,8 +16202,7 @@
         <v>1</v>
       </c>
       <c r="W194" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>28008.147726731742</v>
       </c>
       <c r="X194" s="16"/>
       <c r="Y194" s="17"/>
@@ -16626,8 +16267,7 @@
         <v>141.48863016959999</v>
       </c>
       <c r="S195" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.4783143676385135</v>
       </c>
       <c r="T195" s="15">
         <v>1320.1339240414709</v>
@@ -16637,8 +16277,7 @@
         <v>1</v>
       </c>
       <c r="W195" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27998.05640584484</v>
       </c>
       <c r="X195" s="16"/>
       <c r="Y195" s="17"/>
@@ -16703,8 +16342,7 @@
         <v>173.5380552192</v>
       </c>
       <c r="S196" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.484667951970982</v>
       </c>
       <c r="T196" s="15">
         <v>1490.9749826931859</v>
@@ -16714,8 +16352,7 @@
         <v>1</v>
       </c>
       <c r="W196" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27801.983049744918</v>
       </c>
       <c r="X196" s="16"/>
       <c r="Y196" s="17"/>
@@ -16780,8 +16417,7 @@
         <v>74.56516444159999</v>
       </c>
       <c r="S197" s="15">
-        <f t="shared" si="12"/>
-        <v>4.5000000000000009</v>
+        <v>4.5027528461221777</v>
       </c>
       <c r="T197" s="15">
         <v>458.3798272003587</v>
@@ -16791,8 +16427,7 @@
         <v>1</v>
       </c>
       <c r="W197" s="15">
-        <f t="shared" si="13"/>
-        <v>27916.666666666668</v>
+        <v>27908.063836857684</v>
       </c>
       <c r="X197" s="16"/>
       <c r="Y197" s="17"/>
@@ -16858,7 +16493,7 @@
         <v>6.8740127232000008</v>
       </c>
       <c r="S198" s="15">
-        <v>0.98</v>
+        <v>0.98117629369132831</v>
       </c>
       <c r="T198" s="15">
         <v>5.1029770405798809</v>
@@ -16868,7 +16503,7 @@
         <v>1</v>
       </c>
       <c r="W198" s="15">
-        <v>40086.594535584823</v>
+        <v>40041.447536126245</v>
       </c>
       <c r="X198" s="16"/>
       <c r="Y198" s="17"/>
@@ -16933,8 +16568,7 @@
         <v>143.2085984</v>
       </c>
       <c r="S199" s="15">
-        <f>AVERAGE(0.004, 0.005)*1000</f>
-        <v>4.5000000000000009</v>
+        <v>4.5153231476349003</v>
       </c>
       <c r="T199" s="15">
         <v>52.460169577596993</v>
@@ -16944,8 +16578,7 @@
         <v>1</v>
       </c>
       <c r="W199" s="15">
-        <f>AVERAGE(900,1300,450,700)*1000/30</f>
-        <v>27916.666666666668</v>
+        <v>27801.730624336302</v>
       </c>
       <c r="X199" s="16"/>
       <c r="Y199" s="17"/>
